--- a/development/one_file_rosetta_output/SP112290_rosetta.xlsx
+++ b/development/one_file_rosetta_output/SP112290_rosetta.xlsx
@@ -398,14 +398,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E607"/>
+  <dimension ref="A1:F607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
     <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
     <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -426,10 +427,15 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>N indels</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>Example n</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Indel in context</t>
         </is>
@@ -452,9 +458,12 @@
         </is>
       </c>
       <c r="D2" s="4">
+        <v>13</v>
+      </c>
+      <c r="E2" s="4">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -508,9 +517,12 @@
         </is>
       </c>
       <c r="D3" s="4">
+        <v>13</v>
+      </c>
+      <c r="E3" s="4">
         <v>2</v>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -564,9 +576,12 @@
         </is>
       </c>
       <c r="D4" s="4">
+        <v>13</v>
+      </c>
+      <c r="E4" s="4">
         <v>3</v>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -620,9 +635,12 @@
         </is>
       </c>
       <c r="D5" s="4">
+        <v>13</v>
+      </c>
+      <c r="E5" s="4">
         <v>4</v>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -676,9 +694,12 @@
         </is>
       </c>
       <c r="D6" s="4">
+        <v>13</v>
+      </c>
+      <c r="E6" s="4">
         <v>5</v>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -732,9 +753,12 @@
         </is>
       </c>
       <c r="D7" s="4">
+        <v>3</v>
+      </c>
+      <c r="E7" s="4">
         <v>1</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -788,9 +812,12 @@
         </is>
       </c>
       <c r="D8" s="4">
+        <v>3</v>
+      </c>
+      <c r="E8" s="4">
         <v>2</v>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -844,9 +871,12 @@
         </is>
       </c>
       <c r="D9" s="4">
+        <v>6</v>
+      </c>
+      <c r="E9" s="4">
         <v>1</v>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -900,9 +930,12 @@
         </is>
       </c>
       <c r="D10" s="4">
+        <v>6</v>
+      </c>
+      <c r="E10" s="4">
         <v>2</v>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -956,9 +989,12 @@
         </is>
       </c>
       <c r="D11" s="4">
+        <v>6</v>
+      </c>
+      <c r="E11" s="4">
         <v>3</v>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1012,9 +1048,12 @@
         </is>
       </c>
       <c r="D12" s="4">
+        <v>21</v>
+      </c>
+      <c r="E12" s="4">
         <v>1</v>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1075,9 +1114,12 @@
         </is>
       </c>
       <c r="D13" s="4">
+        <v>21</v>
+      </c>
+      <c r="E13" s="4">
         <v>2</v>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1138,9 +1180,12 @@
         </is>
       </c>
       <c r="D14" s="4">
+        <v>21</v>
+      </c>
+      <c r="E14" s="4">
         <v>3</v>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1201,9 +1246,12 @@
         </is>
       </c>
       <c r="D15" s="4">
+        <v>21</v>
+      </c>
+      <c r="E15" s="4">
         <v>4</v>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1264,9 +1312,12 @@
         </is>
       </c>
       <c r="D16" s="4">
+        <v>21</v>
+      </c>
+      <c r="E16" s="4">
         <v>5</v>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1327,9 +1378,12 @@
         </is>
       </c>
       <c r="D17" s="4">
+        <v>2</v>
+      </c>
+      <c r="E17" s="4">
         <v>1</v>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1355,9 +1409,12 @@
         </is>
       </c>
       <c r="D18" s="4">
+        <v>7</v>
+      </c>
+      <c r="E18" s="4">
         <v>1</v>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1418,9 +1475,12 @@
         </is>
       </c>
       <c r="D19" s="4">
+        <v>7</v>
+      </c>
+      <c r="E19" s="4">
         <v>2</v>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1481,9 +1541,12 @@
         </is>
       </c>
       <c r="D20" s="4">
+        <v>7</v>
+      </c>
+      <c r="E20" s="4">
         <v>3</v>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1544,9 +1607,12 @@
         </is>
       </c>
       <c r="D21" s="4">
+        <v>7</v>
+      </c>
+      <c r="E21" s="4">
         <v>4</v>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1607,9 +1673,12 @@
         </is>
       </c>
       <c r="D22" s="4">
+        <v>17</v>
+      </c>
+      <c r="E22" s="4">
         <v>1</v>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1678,9 +1747,12 @@
         </is>
       </c>
       <c r="D23" s="4">
+        <v>17</v>
+      </c>
+      <c r="E23" s="4">
         <v>2</v>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1749,9 +1821,12 @@
         </is>
       </c>
       <c r="D24" s="4">
+        <v>17</v>
+      </c>
+      <c r="E24" s="4">
         <v>3</v>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1820,9 +1895,12 @@
         </is>
       </c>
       <c r="D25" s="4">
+        <v>17</v>
+      </c>
+      <c r="E25" s="4">
         <v>4</v>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1891,9 +1969,12 @@
         </is>
       </c>
       <c r="D26" s="4">
+        <v>17</v>
+      </c>
+      <c r="E26" s="4">
         <v>5</v>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1964,7 +2045,10 @@
       <c r="D27" s="4">
         <v>1</v>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="4">
+        <v>1</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2033,9 +2117,12 @@
         </is>
       </c>
       <c r="D28" s="4">
+        <v>8</v>
+      </c>
+      <c r="E28" s="4">
         <v>1</v>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2104,9 +2191,12 @@
         </is>
       </c>
       <c r="D29" s="4">
+        <v>8</v>
+      </c>
+      <c r="E29" s="4">
         <v>2</v>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2175,9 +2265,12 @@
         </is>
       </c>
       <c r="D30" s="4">
+        <v>8</v>
+      </c>
+      <c r="E30" s="4">
         <v>3</v>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2246,9 +2339,12 @@
         </is>
       </c>
       <c r="D31" s="4">
+        <v>8</v>
+      </c>
+      <c r="E31" s="4">
         <v>4</v>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2317,9 +2413,12 @@
         </is>
       </c>
       <c r="D32" s="4">
+        <v>6</v>
+      </c>
+      <c r="E32" s="4">
         <v>1</v>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2395,9 +2494,12 @@
         </is>
       </c>
       <c r="D33" s="4">
+        <v>6</v>
+      </c>
+      <c r="E33" s="4">
         <v>2</v>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2473,9 +2575,12 @@
         </is>
       </c>
       <c r="D34" s="4">
+        <v>6</v>
+      </c>
+      <c r="E34" s="4">
         <v>3</v>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2551,9 +2656,12 @@
         </is>
       </c>
       <c r="D35" s="4">
+        <v>4</v>
+      </c>
+      <c r="E35" s="4">
         <v>1</v>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2629,9 +2737,12 @@
         </is>
       </c>
       <c r="D36" s="4">
+        <v>4</v>
+      </c>
+      <c r="E36" s="4">
         <v>2</v>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2707,9 +2818,12 @@
         </is>
       </c>
       <c r="D37" s="4">
+        <v>4</v>
+      </c>
+      <c r="E37" s="4">
         <v>1</v>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2795,7 +2909,10 @@
       <c r="D38" s="4">
         <v>1</v>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E38" s="4">
+        <v>1</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2821,9 +2938,12 @@
         </is>
       </c>
       <c r="D39" s="4">
+        <v>2</v>
+      </c>
+      <c r="E39" s="4">
         <v>1</v>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2909,7 +3029,10 @@
       <c r="D40" s="4">
         <v>1</v>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E40" s="4">
+        <v>1</v>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3002,7 +3125,10 @@
       <c r="D41" s="4">
         <v>1</v>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="E41" s="4">
+        <v>1</v>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3030,7 +3156,10 @@
       <c r="D42" s="4">
         <v>1</v>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="E42" s="4">
+        <v>1</v>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3129,9 +3258,12 @@
         </is>
       </c>
       <c r="D43" s="4">
+        <v>5</v>
+      </c>
+      <c r="E43" s="4">
         <v>1</v>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3185,9 +3317,12 @@
         </is>
       </c>
       <c r="D44" s="4">
+        <v>5</v>
+      </c>
+      <c r="E44" s="4">
         <v>2</v>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3243,7 +3378,10 @@
       <c r="D45" s="4">
         <v>1</v>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E45" s="4">
+        <v>1</v>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3269,9 +3407,12 @@
         </is>
       </c>
       <c r="D46" s="4">
+        <v>2</v>
+      </c>
+      <c r="E46" s="4">
         <v>1</v>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3325,9 +3466,12 @@
         </is>
       </c>
       <c r="D47" s="4">
+        <v>14</v>
+      </c>
+      <c r="E47" s="4">
         <v>1</v>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3388,9 +3532,12 @@
         </is>
       </c>
       <c r="D48" s="4">
+        <v>14</v>
+      </c>
+      <c r="E48" s="4">
         <v>2</v>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="F48" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3451,9 +3598,12 @@
         </is>
       </c>
       <c r="D49" s="4">
+        <v>14</v>
+      </c>
+      <c r="E49" s="4">
         <v>3</v>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3514,9 +3664,12 @@
         </is>
       </c>
       <c r="D50" s="4">
+        <v>14</v>
+      </c>
+      <c r="E50" s="4">
         <v>4</v>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3577,9 +3730,12 @@
         </is>
       </c>
       <c r="D51" s="4">
+        <v>3</v>
+      </c>
+      <c r="E51" s="4">
         <v>1</v>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3640,9 +3796,12 @@
         </is>
       </c>
       <c r="D52" s="4">
+        <v>3</v>
+      </c>
+      <c r="E52" s="4">
         <v>2</v>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3703,9 +3862,12 @@
         </is>
       </c>
       <c r="D53" s="4">
+        <v>6</v>
+      </c>
+      <c r="E53" s="4">
         <v>1</v>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3766,9 +3928,12 @@
         </is>
       </c>
       <c r="D54" s="4">
+        <v>6</v>
+      </c>
+      <c r="E54" s="4">
         <v>2</v>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3829,9 +3994,12 @@
         </is>
       </c>
       <c r="D55" s="4">
+        <v>6</v>
+      </c>
+      <c r="E55" s="4">
         <v>3</v>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3892,9 +4060,12 @@
         </is>
       </c>
       <c r="D56" s="4">
+        <v>6</v>
+      </c>
+      <c r="E56" s="4">
         <v>4</v>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3955,9 +4126,12 @@
         </is>
       </c>
       <c r="D57" s="4">
+        <v>6</v>
+      </c>
+      <c r="E57" s="4">
         <v>5</v>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4018,9 +4192,12 @@
         </is>
       </c>
       <c r="D58" s="4">
+        <v>11</v>
+      </c>
+      <c r="E58" s="4">
         <v>1</v>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4089,9 +4266,12 @@
         </is>
       </c>
       <c r="D59" s="4">
+        <v>11</v>
+      </c>
+      <c r="E59" s="4">
         <v>2</v>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4160,9 +4340,12 @@
         </is>
       </c>
       <c r="D60" s="4">
+        <v>11</v>
+      </c>
+      <c r="E60" s="4">
         <v>3</v>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="F60" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4231,9 +4414,12 @@
         </is>
       </c>
       <c r="D61" s="4">
+        <v>11</v>
+      </c>
+      <c r="E61" s="4">
         <v>4</v>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4302,9 +4488,12 @@
         </is>
       </c>
       <c r="D62" s="4">
+        <v>11</v>
+      </c>
+      <c r="E62" s="4">
         <v>5</v>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="F62" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4375,7 +4564,10 @@
       <c r="D63" s="4">
         <v>1</v>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="E63" s="4">
+        <v>1</v>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4401,9 +4593,12 @@
         </is>
       </c>
       <c r="D64" s="4">
+        <v>5</v>
+      </c>
+      <c r="E64" s="4">
         <v>1</v>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="F64" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4472,9 +4667,12 @@
         </is>
       </c>
       <c r="D65" s="4">
+        <v>5</v>
+      </c>
+      <c r="E65" s="4">
         <v>2</v>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4543,9 +4741,12 @@
         </is>
       </c>
       <c r="D66" s="4">
+        <v>5</v>
+      </c>
+      <c r="E66" s="4">
         <v>3</v>
       </c>
-      <c r="E66" s="6" t="inlineStr">
+      <c r="F66" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4614,9 +4815,12 @@
         </is>
       </c>
       <c r="D67" s="4">
+        <v>5</v>
+      </c>
+      <c r="E67" s="4">
         <v>4</v>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4685,9 +4889,12 @@
         </is>
       </c>
       <c r="D68" s="4">
+        <v>8</v>
+      </c>
+      <c r="E68" s="4">
         <v>1</v>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="F68" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4763,9 +4970,12 @@
         </is>
       </c>
       <c r="D69" s="4">
+        <v>8</v>
+      </c>
+      <c r="E69" s="4">
         <v>2</v>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4841,9 +5051,12 @@
         </is>
       </c>
       <c r="D70" s="4">
+        <v>8</v>
+      </c>
+      <c r="E70" s="4">
         <v>3</v>
       </c>
-      <c r="E70" s="6" t="inlineStr">
+      <c r="F70" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4919,9 +5132,12 @@
         </is>
       </c>
       <c r="D71" s="4">
+        <v>8</v>
+      </c>
+      <c r="E71" s="4">
         <v>4</v>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4999,7 +5215,10 @@
       <c r="D72" s="4">
         <v>1</v>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="E72" s="4">
+        <v>1</v>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5025,9 +5244,12 @@
         </is>
       </c>
       <c r="D73" s="4">
+        <v>4</v>
+      </c>
+      <c r="E73" s="4">
         <v>1</v>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5103,9 +5325,12 @@
         </is>
       </c>
       <c r="D74" s="4">
+        <v>4</v>
+      </c>
+      <c r="E74" s="4">
         <v>2</v>
       </c>
-      <c r="E74" s="6" t="inlineStr">
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5181,9 +5406,12 @@
         </is>
       </c>
       <c r="D75" s="4">
+        <v>3</v>
+      </c>
+      <c r="E75" s="4">
         <v>1</v>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5267,9 +5495,12 @@
         </is>
       </c>
       <c r="D76" s="4">
+        <v>2</v>
+      </c>
+      <c r="E76" s="4">
         <v>1</v>
       </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="F76" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5355,7 +5586,10 @@
       <c r="D77" s="4">
         <v>2</v>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="E77" s="4">
+        <v>2</v>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5439,9 +5673,12 @@
         </is>
       </c>
       <c r="D78" s="4">
+        <v>3</v>
+      </c>
+      <c r="E78" s="4">
         <v>1</v>
       </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="F78" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5532,9 +5769,12 @@
         </is>
       </c>
       <c r="D79" s="4">
+        <v>3</v>
+      </c>
+      <c r="E79" s="4">
         <v>2</v>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5627,7 +5867,10 @@
       <c r="D80" s="4">
         <v>1</v>
       </c>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="E80" s="4">
+        <v>1</v>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5655,7 +5898,10 @@
       <c r="D81" s="4">
         <v>1</v>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="E81" s="4">
+        <v>1</v>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5754,9 +6000,12 @@
         </is>
       </c>
       <c r="D82" s="4">
+        <v>18</v>
+      </c>
+      <c r="E82" s="4">
         <v>1</v>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="F82" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5810,9 +6059,12 @@
         </is>
       </c>
       <c r="D83" s="4">
+        <v>18</v>
+      </c>
+      <c r="E83" s="4">
         <v>2</v>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5866,9 +6118,12 @@
         </is>
       </c>
       <c r="D84" s="4">
+        <v>18</v>
+      </c>
+      <c r="E84" s="4">
         <v>3</v>
       </c>
-      <c r="E84" s="6" t="inlineStr">
+      <c r="F84" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5922,9 +6177,12 @@
         </is>
       </c>
       <c r="D85" s="4">
+        <v>18</v>
+      </c>
+      <c r="E85" s="4">
         <v>4</v>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5978,9 +6236,12 @@
         </is>
       </c>
       <c r="D86" s="4">
+        <v>18</v>
+      </c>
+      <c r="E86" s="4">
         <v>5</v>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6036,7 +6297,10 @@
       <c r="D87" s="4">
         <v>1</v>
       </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="E87" s="4">
+        <v>1</v>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6090,9 +6354,12 @@
         </is>
       </c>
       <c r="D88" s="4">
+        <v>13</v>
+      </c>
+      <c r="E88" s="4">
         <v>1</v>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="F88" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6146,9 +6413,12 @@
         </is>
       </c>
       <c r="D89" s="4">
+        <v>13</v>
+      </c>
+      <c r="E89" s="4">
         <v>2</v>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6202,9 +6472,12 @@
         </is>
       </c>
       <c r="D90" s="4">
+        <v>13</v>
+      </c>
+      <c r="E90" s="4">
         <v>3</v>
       </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="F90" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6258,9 +6531,12 @@
         </is>
       </c>
       <c r="D91" s="4">
+        <v>13</v>
+      </c>
+      <c r="E91" s="4">
         <v>4</v>
       </c>
-      <c r="E91" s="6" t="inlineStr">
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6314,9 +6590,12 @@
         </is>
       </c>
       <c r="D92" s="4">
+        <v>13</v>
+      </c>
+      <c r="E92" s="4">
         <v>5</v>
       </c>
-      <c r="E92" s="6" t="inlineStr">
+      <c r="F92" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6370,9 +6649,12 @@
         </is>
       </c>
       <c r="D93" s="4">
+        <v>30</v>
+      </c>
+      <c r="E93" s="4">
         <v>1</v>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6433,9 +6715,12 @@
         </is>
       </c>
       <c r="D94" s="4">
+        <v>30</v>
+      </c>
+      <c r="E94" s="4">
         <v>2</v>
       </c>
-      <c r="E94" s="6" t="inlineStr">
+      <c r="F94" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6496,9 +6781,12 @@
         </is>
       </c>
       <c r="D95" s="4">
+        <v>30</v>
+      </c>
+      <c r="E95" s="4">
         <v>3</v>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6559,9 +6847,12 @@
         </is>
       </c>
       <c r="D96" s="4">
+        <v>30</v>
+      </c>
+      <c r="E96" s="4">
         <v>4</v>
       </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="F96" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6622,9 +6913,12 @@
         </is>
       </c>
       <c r="D97" s="4">
+        <v>30</v>
+      </c>
+      <c r="E97" s="4">
         <v>5</v>
       </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="F97" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6685,9 +6979,12 @@
         </is>
       </c>
       <c r="D98" s="4">
+        <v>2</v>
+      </c>
+      <c r="E98" s="4">
         <v>1</v>
       </c>
-      <c r="E98" s="6" t="inlineStr">
+      <c r="F98" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6750,7 +7047,10 @@
       <c r="D99" s="4">
         <v>2</v>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="E99" s="4">
+        <v>2</v>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6811,9 +7111,12 @@
         </is>
       </c>
       <c r="D100" s="4">
+        <v>11</v>
+      </c>
+      <c r="E100" s="4">
         <v>1</v>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="F100" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6874,9 +7177,12 @@
         </is>
       </c>
       <c r="D101" s="4">
+        <v>11</v>
+      </c>
+      <c r="E101" s="4">
         <v>2</v>
       </c>
-      <c r="E101" s="6" t="inlineStr">
+      <c r="F101" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6937,9 +7243,12 @@
         </is>
       </c>
       <c r="D102" s="4">
+        <v>11</v>
+      </c>
+      <c r="E102" s="4">
         <v>3</v>
       </c>
-      <c r="E102" s="6" t="inlineStr">
+      <c r="F102" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7000,9 +7309,12 @@
         </is>
       </c>
       <c r="D103" s="4">
+        <v>11</v>
+      </c>
+      <c r="E103" s="4">
         <v>4</v>
       </c>
-      <c r="E103" s="6" t="inlineStr">
+      <c r="F103" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7063,9 +7375,12 @@
         </is>
       </c>
       <c r="D104" s="4">
+        <v>11</v>
+      </c>
+      <c r="E104" s="4">
         <v>5</v>
       </c>
-      <c r="E104" s="6" t="inlineStr">
+      <c r="F104" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7126,9 +7441,12 @@
         </is>
       </c>
       <c r="D105" s="4">
+        <v>13</v>
+      </c>
+      <c r="E105" s="4">
         <v>1</v>
       </c>
-      <c r="E105" s="6" t="inlineStr">
+      <c r="F105" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7197,9 +7515,12 @@
         </is>
       </c>
       <c r="D106" s="4">
+        <v>13</v>
+      </c>
+      <c r="E106" s="4">
         <v>2</v>
       </c>
-      <c r="E106" s="6" t="inlineStr">
+      <c r="F106" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7268,9 +7589,12 @@
         </is>
       </c>
       <c r="D107" s="4">
+        <v>13</v>
+      </c>
+      <c r="E107" s="4">
         <v>3</v>
       </c>
-      <c r="E107" s="6" t="inlineStr">
+      <c r="F107" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7339,9 +7663,12 @@
         </is>
       </c>
       <c r="D108" s="4">
+        <v>13</v>
+      </c>
+      <c r="E108" s="4">
         <v>4</v>
       </c>
-      <c r="E108" s="6" t="inlineStr">
+      <c r="F108" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7410,9 +7737,12 @@
         </is>
       </c>
       <c r="D109" s="4">
+        <v>13</v>
+      </c>
+      <c r="E109" s="4">
         <v>5</v>
       </c>
-      <c r="E109" s="6" t="inlineStr">
+      <c r="F109" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7483,7 +7813,10 @@
       <c r="D110" s="4">
         <v>1</v>
       </c>
-      <c r="E110" s="6" t="inlineStr">
+      <c r="E110" s="4">
+        <v>1</v>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7552,9 +7885,12 @@
         </is>
       </c>
       <c r="D111" s="4">
+        <v>6</v>
+      </c>
+      <c r="E111" s="4">
         <v>1</v>
       </c>
-      <c r="E111" s="6" t="inlineStr">
+      <c r="F111" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7623,9 +7959,12 @@
         </is>
       </c>
       <c r="D112" s="4">
+        <v>6</v>
+      </c>
+      <c r="E112" s="4">
         <v>2</v>
       </c>
-      <c r="E112" s="6" t="inlineStr">
+      <c r="F112" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7694,9 +8033,12 @@
         </is>
       </c>
       <c r="D113" s="4">
+        <v>6</v>
+      </c>
+      <c r="E113" s="4">
         <v>3</v>
       </c>
-      <c r="E113" s="6" t="inlineStr">
+      <c r="F113" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7765,9 +8107,12 @@
         </is>
       </c>
       <c r="D114" s="4">
+        <v>6</v>
+      </c>
+      <c r="E114" s="4">
         <v>1</v>
       </c>
-      <c r="E114" s="6" t="inlineStr">
+      <c r="F114" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7843,9 +8188,12 @@
         </is>
       </c>
       <c r="D115" s="4">
+        <v>6</v>
+      </c>
+      <c r="E115" s="4">
         <v>2</v>
       </c>
-      <c r="E115" s="6" t="inlineStr">
+      <c r="F115" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7921,9 +8269,12 @@
         </is>
       </c>
       <c r="D116" s="4">
+        <v>2</v>
+      </c>
+      <c r="E116" s="4">
         <v>1</v>
       </c>
-      <c r="E116" s="6" t="inlineStr">
+      <c r="F116" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7999,9 +8350,12 @@
         </is>
       </c>
       <c r="D117" s="4">
+        <v>6</v>
+      </c>
+      <c r="E117" s="4">
         <v>1</v>
       </c>
-      <c r="E117" s="6" t="inlineStr">
+      <c r="F117" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8077,9 +8431,12 @@
         </is>
       </c>
       <c r="D118" s="4">
+        <v>4</v>
+      </c>
+      <c r="E118" s="4">
         <v>1</v>
       </c>
-      <c r="E118" s="6" t="inlineStr">
+      <c r="F118" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8163,9 +8520,12 @@
         </is>
       </c>
       <c r="D119" s="4">
+        <v>4</v>
+      </c>
+      <c r="E119" s="4">
         <v>2</v>
       </c>
-      <c r="E119" s="6" t="inlineStr">
+      <c r="F119" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8249,9 +8609,12 @@
         </is>
       </c>
       <c r="D120" s="4">
+        <v>4</v>
+      </c>
+      <c r="E120" s="4">
         <v>3</v>
       </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="F120" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8337,7 +8700,10 @@
       <c r="D121" s="4">
         <v>1</v>
       </c>
-      <c r="E121" s="6" t="inlineStr">
+      <c r="E121" s="4">
+        <v>1</v>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8421,9 +8787,12 @@
         </is>
       </c>
       <c r="D122" s="4">
+        <v>12</v>
+      </c>
+      <c r="E122" s="4">
         <v>1</v>
       </c>
-      <c r="E122" s="6" t="inlineStr">
+      <c r="F122" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8477,9 +8846,12 @@
         </is>
       </c>
       <c r="D123" s="4">
+        <v>12</v>
+      </c>
+      <c r="E123" s="4">
         <v>2</v>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="F123" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8533,9 +8905,12 @@
         </is>
       </c>
       <c r="D124" s="4">
+        <v>12</v>
+      </c>
+      <c r="E124" s="4">
         <v>3</v>
       </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="F124" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8589,9 +8964,12 @@
         </is>
       </c>
       <c r="D125" s="4">
+        <v>12</v>
+      </c>
+      <c r="E125" s="4">
         <v>4</v>
       </c>
-      <c r="E125" s="6" t="inlineStr">
+      <c r="F125" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8645,9 +9023,12 @@
         </is>
       </c>
       <c r="D126" s="4">
+        <v>12</v>
+      </c>
+      <c r="E126" s="4">
         <v>5</v>
       </c>
-      <c r="E126" s="6" t="inlineStr">
+      <c r="F126" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8701,9 +9082,12 @@
         </is>
       </c>
       <c r="D127" s="4">
+        <v>8</v>
+      </c>
+      <c r="E127" s="4">
         <v>1</v>
       </c>
-      <c r="E127" s="6" t="inlineStr">
+      <c r="F127" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8757,9 +9141,12 @@
         </is>
       </c>
       <c r="D128" s="4">
+        <v>8</v>
+      </c>
+      <c r="E128" s="4">
         <v>2</v>
       </c>
-      <c r="E128" s="6" t="inlineStr">
+      <c r="F128" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8813,9 +9200,12 @@
         </is>
       </c>
       <c r="D129" s="4">
+        <v>8</v>
+      </c>
+      <c r="E129" s="4">
         <v>3</v>
       </c>
-      <c r="E129" s="6" t="inlineStr">
+      <c r="F129" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8869,9 +9259,12 @@
         </is>
       </c>
       <c r="D130" s="4">
+        <v>8</v>
+      </c>
+      <c r="E130" s="4">
         <v>4</v>
       </c>
-      <c r="E130" s="6" t="inlineStr">
+      <c r="F130" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8925,9 +9318,12 @@
         </is>
       </c>
       <c r="D131" s="4">
+        <v>3</v>
+      </c>
+      <c r="E131" s="4">
         <v>1</v>
       </c>
-      <c r="E131" s="6" t="inlineStr">
+      <c r="F131" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8953,9 +9349,12 @@
         </is>
       </c>
       <c r="D132" s="4">
+        <v>4</v>
+      </c>
+      <c r="E132" s="4">
         <v>1</v>
       </c>
-      <c r="E132" s="6" t="inlineStr">
+      <c r="F132" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9016,9 +9415,12 @@
         </is>
       </c>
       <c r="D133" s="4">
+        <v>9</v>
+      </c>
+      <c r="E133" s="4">
         <v>1</v>
       </c>
-      <c r="E133" s="6" t="inlineStr">
+      <c r="F133" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9079,9 +9481,12 @@
         </is>
       </c>
       <c r="D134" s="4">
+        <v>9</v>
+      </c>
+      <c r="E134" s="4">
         <v>2</v>
       </c>
-      <c r="E134" s="6" t="inlineStr">
+      <c r="F134" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9142,9 +9547,12 @@
         </is>
       </c>
       <c r="D135" s="4">
+        <v>9</v>
+      </c>
+      <c r="E135" s="4">
         <v>3</v>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="F135" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9205,9 +9613,12 @@
         </is>
       </c>
       <c r="D136" s="4">
+        <v>9</v>
+      </c>
+      <c r="E136" s="4">
         <v>4</v>
       </c>
-      <c r="E136" s="6" t="inlineStr">
+      <c r="F136" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9268,9 +9679,12 @@
         </is>
       </c>
       <c r="D137" s="4">
+        <v>9</v>
+      </c>
+      <c r="E137" s="4">
         <v>5</v>
       </c>
-      <c r="E137" s="6" t="inlineStr">
+      <c r="F137" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9331,9 +9745,12 @@
         </is>
       </c>
       <c r="D138" s="4">
+        <v>9</v>
+      </c>
+      <c r="E138" s="4">
         <v>1</v>
       </c>
-      <c r="E138" s="6" t="inlineStr">
+      <c r="F138" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9394,9 +9811,12 @@
         </is>
       </c>
       <c r="D139" s="4">
+        <v>9</v>
+      </c>
+      <c r="E139" s="4">
         <v>2</v>
       </c>
-      <c r="E139" s="6" t="inlineStr">
+      <c r="F139" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9457,9 +9877,12 @@
         </is>
       </c>
       <c r="D140" s="4">
+        <v>9</v>
+      </c>
+      <c r="E140" s="4">
         <v>3</v>
       </c>
-      <c r="E140" s="6" t="inlineStr">
+      <c r="F140" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9520,9 +9943,12 @@
         </is>
       </c>
       <c r="D141" s="4">
+        <v>9</v>
+      </c>
+      <c r="E141" s="4">
         <v>4</v>
       </c>
-      <c r="E141" s="6" t="inlineStr">
+      <c r="F141" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9583,9 +10009,12 @@
         </is>
       </c>
       <c r="D142" s="4">
+        <v>9</v>
+      </c>
+      <c r="E142" s="4">
         <v>5</v>
       </c>
-      <c r="E142" s="6" t="inlineStr">
+      <c r="F142" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9646,9 +10075,12 @@
         </is>
       </c>
       <c r="D143" s="4">
+        <v>9</v>
+      </c>
+      <c r="E143" s="4">
         <v>1</v>
       </c>
-      <c r="E143" s="6" t="inlineStr">
+      <c r="F143" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9717,9 +10149,12 @@
         </is>
       </c>
       <c r="D144" s="4">
+        <v>9</v>
+      </c>
+      <c r="E144" s="4">
         <v>2</v>
       </c>
-      <c r="E144" s="6" t="inlineStr">
+      <c r="F144" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9788,9 +10223,12 @@
         </is>
       </c>
       <c r="D145" s="4">
+        <v>9</v>
+      </c>
+      <c r="E145" s="4">
         <v>3</v>
       </c>
-      <c r="E145" s="6" t="inlineStr">
+      <c r="F145" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9859,9 +10297,12 @@
         </is>
       </c>
       <c r="D146" s="4">
+        <v>9</v>
+      </c>
+      <c r="E146" s="4">
         <v>4</v>
       </c>
-      <c r="E146" s="6" t="inlineStr">
+      <c r="F146" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9930,9 +10371,12 @@
         </is>
       </c>
       <c r="D147" s="4">
+        <v>9</v>
+      </c>
+      <c r="E147" s="4">
         <v>5</v>
       </c>
-      <c r="E147" s="6" t="inlineStr">
+      <c r="F147" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10001,9 +10445,12 @@
         </is>
       </c>
       <c r="D148" s="4">
+        <v>5</v>
+      </c>
+      <c r="E148" s="4">
         <v>1</v>
       </c>
-      <c r="E148" s="6" t="inlineStr">
+      <c r="F148" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10029,9 +10476,12 @@
         </is>
       </c>
       <c r="D149" s="4">
+        <v>6</v>
+      </c>
+      <c r="E149" s="4">
         <v>1</v>
       </c>
-      <c r="E149" s="6" t="inlineStr">
+      <c r="F149" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10100,9 +10550,12 @@
         </is>
       </c>
       <c r="D150" s="4">
+        <v>6</v>
+      </c>
+      <c r="E150" s="4">
         <v>2</v>
       </c>
-      <c r="E150" s="6" t="inlineStr">
+      <c r="F150" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10171,9 +10624,12 @@
         </is>
       </c>
       <c r="D151" s="4">
+        <v>6</v>
+      </c>
+      <c r="E151" s="4">
         <v>3</v>
       </c>
-      <c r="E151" s="6" t="inlineStr">
+      <c r="F151" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10242,9 +10698,12 @@
         </is>
       </c>
       <c r="D152" s="4">
+        <v>4</v>
+      </c>
+      <c r="E152" s="4">
         <v>1</v>
       </c>
-      <c r="E152" s="6" t="inlineStr">
+      <c r="F152" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10320,9 +10779,12 @@
         </is>
       </c>
       <c r="D153" s="4">
+        <v>4</v>
+      </c>
+      <c r="E153" s="4">
         <v>2</v>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="F153" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10398,9 +10860,12 @@
         </is>
       </c>
       <c r="D154" s="4">
+        <v>2</v>
+      </c>
+      <c r="E154" s="4">
         <v>1</v>
       </c>
-      <c r="E154" s="6" t="inlineStr">
+      <c r="F154" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10478,7 +10943,10 @@
       <c r="D155" s="4">
         <v>2</v>
       </c>
-      <c r="E155" s="6" t="inlineStr">
+      <c r="E155" s="4">
+        <v>2</v>
+      </c>
+      <c r="F155" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10554,9 +11022,12 @@
         </is>
       </c>
       <c r="D156" s="4">
+        <v>3</v>
+      </c>
+      <c r="E156" s="4">
         <v>1</v>
       </c>
-      <c r="E156" s="6" t="inlineStr">
+      <c r="F156" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10632,9 +11103,12 @@
         </is>
       </c>
       <c r="D157" s="4">
+        <v>5</v>
+      </c>
+      <c r="E157" s="4">
         <v>1</v>
       </c>
-      <c r="E157" s="6" t="inlineStr">
+      <c r="F157" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10718,9 +11192,12 @@
         </is>
       </c>
       <c r="D158" s="4">
+        <v>5</v>
+      </c>
+      <c r="E158" s="4">
         <v>2</v>
       </c>
-      <c r="E158" s="6" t="inlineStr">
+      <c r="F158" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10804,9 +11281,12 @@
         </is>
       </c>
       <c r="D159" s="4">
+        <v>3</v>
+      </c>
+      <c r="E159" s="4">
         <v>1</v>
       </c>
-      <c r="E159" s="6" t="inlineStr">
+      <c r="F159" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10890,9 +11370,12 @@
         </is>
       </c>
       <c r="D160" s="4">
+        <v>3</v>
+      </c>
+      <c r="E160" s="4">
         <v>2</v>
       </c>
-      <c r="E160" s="6" t="inlineStr">
+      <c r="F160" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10976,9 +11459,12 @@
         </is>
       </c>
       <c r="D161" s="4">
+        <v>3</v>
+      </c>
+      <c r="E161" s="4">
         <v>1</v>
       </c>
-      <c r="E161" s="6" t="inlineStr">
+      <c r="F161" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11062,9 +11548,12 @@
         </is>
       </c>
       <c r="D162" s="4">
+        <v>2</v>
+      </c>
+      <c r="E162" s="4">
         <v>1</v>
       </c>
-      <c r="E162" s="6" t="inlineStr">
+      <c r="F162" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11155,9 +11644,12 @@
         </is>
       </c>
       <c r="D163" s="4">
+        <v>3</v>
+      </c>
+      <c r="E163" s="4">
         <v>1</v>
       </c>
-      <c r="E163" s="6" t="inlineStr">
+      <c r="F163" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11248,9 +11740,12 @@
         </is>
       </c>
       <c r="D164" s="4">
+        <v>3</v>
+      </c>
+      <c r="E164" s="4">
         <v>1</v>
       </c>
-      <c r="E164" s="6" t="inlineStr">
+      <c r="F164" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11349,9 +11844,12 @@
         </is>
       </c>
       <c r="D165" s="4">
+        <v>3</v>
+      </c>
+      <c r="E165" s="4">
         <v>2</v>
       </c>
-      <c r="E165" s="6" t="inlineStr">
+      <c r="F165" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11452,7 +11950,10 @@
       <c r="D166" s="4">
         <v>1</v>
       </c>
-      <c r="E166" s="6" t="inlineStr">
+      <c r="E166" s="4">
+        <v>1</v>
+      </c>
+      <c r="F166" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11553,7 +12054,10 @@
       <c r="D167" s="4">
         <v>1</v>
       </c>
-      <c r="E167" s="6" t="inlineStr">
+      <c r="E167" s="4">
+        <v>1</v>
+      </c>
+      <c r="F167" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -11579,9 +12083,12 @@
         </is>
       </c>
       <c r="D168" s="4">
+        <v>7</v>
+      </c>
+      <c r="E168" s="4">
         <v>1</v>
       </c>
-      <c r="E168" s="6" t="inlineStr">
+      <c r="F168" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11635,9 +12142,12 @@
         </is>
       </c>
       <c r="D169" s="4">
+        <v>7</v>
+      </c>
+      <c r="E169" s="4">
         <v>2</v>
       </c>
-      <c r="E169" s="6" t="inlineStr">
+      <c r="F169" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11691,9 +12201,12 @@
         </is>
       </c>
       <c r="D170" s="4">
+        <v>7</v>
+      </c>
+      <c r="E170" s="4">
         <v>3</v>
       </c>
-      <c r="E170" s="6" t="inlineStr">
+      <c r="F170" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11747,9 +12260,12 @@
         </is>
       </c>
       <c r="D171" s="4">
+        <v>7</v>
+      </c>
+      <c r="E171" s="4">
         <v>4</v>
       </c>
-      <c r="E171" s="6" t="inlineStr">
+      <c r="F171" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11803,9 +12319,12 @@
         </is>
       </c>
       <c r="D172" s="4">
+        <v>7</v>
+      </c>
+      <c r="E172" s="4">
         <v>5</v>
       </c>
-      <c r="E172" s="6" t="inlineStr">
+      <c r="F172" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11859,9 +12378,12 @@
         </is>
       </c>
       <c r="D173" s="4">
+        <v>9</v>
+      </c>
+      <c r="E173" s="4">
         <v>1</v>
       </c>
-      <c r="E173" s="6" t="inlineStr">
+      <c r="F173" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11915,9 +12437,12 @@
         </is>
       </c>
       <c r="D174" s="4">
+        <v>9</v>
+      </c>
+      <c r="E174" s="4">
         <v>2</v>
       </c>
-      <c r="E174" s="6" t="inlineStr">
+      <c r="F174" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11971,9 +12496,12 @@
         </is>
       </c>
       <c r="D175" s="4">
+        <v>9</v>
+      </c>
+      <c r="E175" s="4">
         <v>3</v>
       </c>
-      <c r="E175" s="6" t="inlineStr">
+      <c r="F175" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12027,9 +12555,12 @@
         </is>
       </c>
       <c r="D176" s="4">
+        <v>9</v>
+      </c>
+      <c r="E176" s="4">
         <v>4</v>
       </c>
-      <c r="E176" s="6" t="inlineStr">
+      <c r="F176" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12083,9 +12614,12 @@
         </is>
       </c>
       <c r="D177" s="4">
+        <v>12</v>
+      </c>
+      <c r="E177" s="4">
         <v>1</v>
       </c>
-      <c r="E177" s="6" t="inlineStr">
+      <c r="F177" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12139,9 +12673,12 @@
         </is>
       </c>
       <c r="D178" s="4">
+        <v>12</v>
+      </c>
+      <c r="E178" s="4">
         <v>2</v>
       </c>
-      <c r="E178" s="6" t="inlineStr">
+      <c r="F178" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12195,9 +12732,12 @@
         </is>
       </c>
       <c r="D179" s="4">
+        <v>12</v>
+      </c>
+      <c r="E179" s="4">
         <v>3</v>
       </c>
-      <c r="E179" s="6" t="inlineStr">
+      <c r="F179" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12251,9 +12791,12 @@
         </is>
       </c>
       <c r="D180" s="4">
+        <v>12</v>
+      </c>
+      <c r="E180" s="4">
         <v>4</v>
       </c>
-      <c r="E180" s="6" t="inlineStr">
+      <c r="F180" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12307,9 +12850,12 @@
         </is>
       </c>
       <c r="D181" s="4">
+        <v>12</v>
+      </c>
+      <c r="E181" s="4">
         <v>5</v>
       </c>
-      <c r="E181" s="6" t="inlineStr">
+      <c r="F181" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12363,9 +12909,12 @@
         </is>
       </c>
       <c r="D182" s="4">
+        <v>4</v>
+      </c>
+      <c r="E182" s="4">
         <v>1</v>
       </c>
-      <c r="E182" s="6" t="inlineStr">
+      <c r="F182" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12426,9 +12975,12 @@
         </is>
       </c>
       <c r="D183" s="4">
+        <v>4</v>
+      </c>
+      <c r="E183" s="4">
         <v>2</v>
       </c>
-      <c r="E183" s="6" t="inlineStr">
+      <c r="F183" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12489,9 +13041,12 @@
         </is>
       </c>
       <c r="D184" s="4">
+        <v>2</v>
+      </c>
+      <c r="E184" s="4">
         <v>1</v>
       </c>
-      <c r="E184" s="6" t="inlineStr">
+      <c r="F184" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12552,9 +13107,12 @@
         </is>
       </c>
       <c r="D185" s="4">
+        <v>5</v>
+      </c>
+      <c r="E185" s="4">
         <v>1</v>
       </c>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="F185" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12615,9 +13173,12 @@
         </is>
       </c>
       <c r="D186" s="4">
+        <v>4</v>
+      </c>
+      <c r="E186" s="4">
         <v>1</v>
       </c>
-      <c r="E186" s="6" t="inlineStr">
+      <c r="F186" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12686,9 +13247,12 @@
         </is>
       </c>
       <c r="D187" s="4">
+        <v>6</v>
+      </c>
+      <c r="E187" s="4">
         <v>1</v>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="F187" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12757,9 +13321,12 @@
         </is>
       </c>
       <c r="D188" s="4">
+        <v>6</v>
+      </c>
+      <c r="E188" s="4">
         <v>2</v>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="F188" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12828,9 +13395,12 @@
         </is>
       </c>
       <c r="D189" s="4">
+        <v>6</v>
+      </c>
+      <c r="E189" s="4">
         <v>3</v>
       </c>
-      <c r="E189" s="6" t="inlineStr">
+      <c r="F189" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12899,9 +13469,12 @@
         </is>
       </c>
       <c r="D190" s="4">
+        <v>3</v>
+      </c>
+      <c r="E190" s="4">
         <v>1</v>
       </c>
-      <c r="E190" s="6" t="inlineStr">
+      <c r="F190" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12970,9 +13543,12 @@
         </is>
       </c>
       <c r="D191" s="4">
+        <v>3</v>
+      </c>
+      <c r="E191" s="4">
         <v>2</v>
       </c>
-      <c r="E191" s="6" t="inlineStr">
+      <c r="F191" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13041,9 +13617,12 @@
         </is>
       </c>
       <c r="D192" s="4">
+        <v>5</v>
+      </c>
+      <c r="E192" s="4">
         <v>1</v>
       </c>
-      <c r="E192" s="6" t="inlineStr">
+      <c r="F192" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13119,9 +13698,12 @@
         </is>
       </c>
       <c r="D193" s="4">
+        <v>5</v>
+      </c>
+      <c r="E193" s="4">
         <v>2</v>
       </c>
-      <c r="E193" s="6" t="inlineStr">
+      <c r="F193" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13197,9 +13779,12 @@
         </is>
       </c>
       <c r="D194" s="4">
+        <v>5</v>
+      </c>
+      <c r="E194" s="4">
         <v>3</v>
       </c>
-      <c r="E194" s="6" t="inlineStr">
+      <c r="F194" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13275,9 +13860,12 @@
         </is>
       </c>
       <c r="D195" s="4">
+        <v>5</v>
+      </c>
+      <c r="E195" s="4">
         <v>4</v>
       </c>
-      <c r="E195" s="6" t="inlineStr">
+      <c r="F195" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13355,7 +13943,10 @@
       <c r="D196" s="4">
         <v>1</v>
       </c>
-      <c r="E196" s="6" t="inlineStr">
+      <c r="E196" s="4">
+        <v>1</v>
+      </c>
+      <c r="F196" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -13381,9 +13972,12 @@
         </is>
       </c>
       <c r="D197" s="4">
+        <v>3</v>
+      </c>
+      <c r="E197" s="4">
         <v>1</v>
       </c>
-      <c r="E197" s="6" t="inlineStr">
+      <c r="F197" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13459,9 +14053,12 @@
         </is>
       </c>
       <c r="D198" s="4">
+        <v>3</v>
+      </c>
+      <c r="E198" s="4">
         <v>1</v>
       </c>
-      <c r="E198" s="6" t="inlineStr">
+      <c r="F198" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13545,9 +14142,12 @@
         </is>
       </c>
       <c r="D199" s="4">
+        <v>3</v>
+      </c>
+      <c r="E199" s="4">
         <v>1</v>
       </c>
-      <c r="E199" s="6" t="inlineStr">
+      <c r="F199" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13631,9 +14231,12 @@
         </is>
       </c>
       <c r="D200" s="4">
+        <v>3</v>
+      </c>
+      <c r="E200" s="4">
         <v>2</v>
       </c>
-      <c r="E200" s="6" t="inlineStr">
+      <c r="F200" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13717,9 +14320,12 @@
         </is>
       </c>
       <c r="D201" s="4">
+        <v>3</v>
+      </c>
+      <c r="E201" s="4">
         <v>1</v>
       </c>
-      <c r="E201" s="6" t="inlineStr">
+      <c r="F201" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13803,9 +14409,12 @@
         </is>
       </c>
       <c r="D202" s="4">
+        <v>3</v>
+      </c>
+      <c r="E202" s="4">
         <v>1</v>
       </c>
-      <c r="E202" s="6" t="inlineStr">
+      <c r="F202" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13896,9 +14505,12 @@
         </is>
       </c>
       <c r="D203" s="4">
+        <v>3</v>
+      </c>
+      <c r="E203" s="4">
         <v>2</v>
       </c>
-      <c r="E203" s="6" t="inlineStr">
+      <c r="F203" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13991,7 +14603,10 @@
       <c r="D204" s="4">
         <v>1</v>
       </c>
-      <c r="E204" s="6" t="inlineStr">
+      <c r="E204" s="4">
+        <v>1</v>
+      </c>
+      <c r="F204" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14082,9 +14697,12 @@
         </is>
       </c>
       <c r="D205" s="4">
+        <v>2</v>
+      </c>
+      <c r="E205" s="4">
         <v>1</v>
       </c>
-      <c r="E205" s="6" t="inlineStr">
+      <c r="F205" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14185,7 +14803,10 @@
       <c r="D206" s="4">
         <v>2</v>
       </c>
-      <c r="E206" s="6" t="inlineStr">
+      <c r="E206" s="4">
+        <v>2</v>
+      </c>
+      <c r="F206" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14286,7 +14907,10 @@
       <c r="D207" s="4">
         <v>1</v>
       </c>
-      <c r="E207" s="6" t="inlineStr">
+      <c r="E207" s="4">
+        <v>1</v>
+      </c>
+      <c r="F207" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14392,9 +15016,12 @@
         </is>
       </c>
       <c r="D208" s="4">
+        <v>2</v>
+      </c>
+      <c r="E208" s="4">
         <v>1</v>
       </c>
-      <c r="E208" s="6" t="inlineStr">
+      <c r="F208" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14448,9 +15075,12 @@
         </is>
       </c>
       <c r="D209" s="4">
+        <v>2</v>
+      </c>
+      <c r="E209" s="4">
         <v>1</v>
       </c>
-      <c r="E209" s="6" t="inlineStr">
+      <c r="F209" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14506,7 +15136,10 @@
       <c r="D210" s="4">
         <v>2</v>
       </c>
-      <c r="E210" s="6" t="inlineStr">
+      <c r="E210" s="4">
+        <v>2</v>
+      </c>
+      <c r="F210" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14560,9 +15193,12 @@
         </is>
       </c>
       <c r="D211" s="4">
+        <v>3</v>
+      </c>
+      <c r="E211" s="4">
         <v>1</v>
       </c>
-      <c r="E211" s="6" t="inlineStr">
+      <c r="F211" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14616,9 +15252,12 @@
         </is>
       </c>
       <c r="D212" s="4">
+        <v>2</v>
+      </c>
+      <c r="E212" s="4">
         <v>1</v>
       </c>
-      <c r="E212" s="6" t="inlineStr">
+      <c r="F212" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14681,7 +15320,10 @@
       <c r="D213" s="4">
         <v>1</v>
       </c>
-      <c r="E213" s="6" t="inlineStr">
+      <c r="E213" s="4">
+        <v>1</v>
+      </c>
+      <c r="F213" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -14707,9 +15349,12 @@
         </is>
       </c>
       <c r="D214" s="4">
+        <v>5</v>
+      </c>
+      <c r="E214" s="4">
         <v>1</v>
       </c>
-      <c r="E214" s="6" t="inlineStr">
+      <c r="F214" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14770,9 +15415,12 @@
         </is>
       </c>
       <c r="D215" s="4">
+        <v>5</v>
+      </c>
+      <c r="E215" s="4">
         <v>2</v>
       </c>
-      <c r="E215" s="6" t="inlineStr">
+      <c r="F215" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14833,9 +15481,12 @@
         </is>
       </c>
       <c r="D216" s="4">
+        <v>5</v>
+      </c>
+      <c r="E216" s="4">
         <v>3</v>
       </c>
-      <c r="E216" s="6" t="inlineStr">
+      <c r="F216" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14896,9 +15547,12 @@
         </is>
       </c>
       <c r="D217" s="4">
+        <v>3</v>
+      </c>
+      <c r="E217" s="4">
         <v>1</v>
       </c>
-      <c r="E217" s="6" t="inlineStr">
+      <c r="F217" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14967,9 +15621,12 @@
         </is>
       </c>
       <c r="D218" s="4">
+        <v>3</v>
+      </c>
+      <c r="E218" s="4">
         <v>2</v>
       </c>
-      <c r="E218" s="6" t="inlineStr">
+      <c r="F218" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15038,9 +15695,12 @@
         </is>
       </c>
       <c r="D219" s="4">
+        <v>3</v>
+      </c>
+      <c r="E219" s="4">
         <v>1</v>
       </c>
-      <c r="E219" s="6" t="inlineStr">
+      <c r="F219" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15109,9 +15769,12 @@
         </is>
       </c>
       <c r="D220" s="4">
+        <v>3</v>
+      </c>
+      <c r="E220" s="4">
         <v>1</v>
       </c>
-      <c r="E220" s="6" t="inlineStr">
+      <c r="F220" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -15139,7 +15802,10 @@
       <c r="D221" s="4">
         <v>1</v>
       </c>
-      <c r="E221" s="6" t="inlineStr">
+      <c r="E221" s="4">
+        <v>1</v>
+      </c>
+      <c r="F221" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15215,9 +15881,12 @@
         </is>
       </c>
       <c r="D222" s="4">
+        <v>4</v>
+      </c>
+      <c r="E222" s="4">
         <v>1</v>
       </c>
-      <c r="E222" s="6" t="inlineStr">
+      <c r="F222" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15293,9 +15962,12 @@
         </is>
       </c>
       <c r="D223" s="4">
+        <v>4</v>
+      </c>
+      <c r="E223" s="4">
         <v>2</v>
       </c>
-      <c r="E223" s="6" t="inlineStr">
+      <c r="F223" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15373,7 +16045,10 @@
       <c r="D224" s="4">
         <v>1</v>
       </c>
-      <c r="E224" s="6" t="inlineStr">
+      <c r="E224" s="4">
+        <v>1</v>
+      </c>
+      <c r="F224" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15457,9 +16132,12 @@
         </is>
       </c>
       <c r="D225" s="4">
+        <v>2</v>
+      </c>
+      <c r="E225" s="4">
         <v>1</v>
       </c>
-      <c r="E225" s="6" t="inlineStr">
+      <c r="F225" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15545,7 +16223,10 @@
       <c r="D226" s="4">
         <v>2</v>
       </c>
-      <c r="E226" s="6" t="inlineStr">
+      <c r="E226" s="4">
+        <v>2</v>
+      </c>
+      <c r="F226" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15629,9 +16310,12 @@
         </is>
       </c>
       <c r="D227" s="4">
+        <v>3</v>
+      </c>
+      <c r="E227" s="4">
         <v>1</v>
       </c>
-      <c r="E227" s="6" t="inlineStr">
+      <c r="F227" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15722,9 +16406,12 @@
         </is>
       </c>
       <c r="D228" s="4">
+        <v>3</v>
+      </c>
+      <c r="E228" s="4">
         <v>2</v>
       </c>
-      <c r="E228" s="6" t="inlineStr">
+      <c r="F228" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15817,7 +16504,10 @@
       <c r="D229" s="4">
         <v>3</v>
       </c>
-      <c r="E229" s="6" t="inlineStr">
+      <c r="E229" s="4">
+        <v>3</v>
+      </c>
+      <c r="F229" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15908,9 +16598,12 @@
         </is>
       </c>
       <c r="D230" s="4">
+        <v>2</v>
+      </c>
+      <c r="E230" s="4">
         <v>1</v>
       </c>
-      <c r="E230" s="6" t="inlineStr">
+      <c r="F230" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -15938,7 +16631,10 @@
       <c r="D231" s="4">
         <v>1</v>
       </c>
-      <c r="E231" s="6" t="inlineStr">
+      <c r="E231" s="4">
+        <v>1</v>
+      </c>
+      <c r="F231" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -15966,7 +16662,10 @@
       <c r="D232" s="4">
         <v>1</v>
       </c>
-      <c r="E232" s="6" t="inlineStr">
+      <c r="E232" s="4">
+        <v>1</v>
+      </c>
+      <c r="F232" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16067,7 +16766,10 @@
       <c r="D233" s="4">
         <v>1</v>
       </c>
-      <c r="E233" s="6" t="inlineStr">
+      <c r="E233" s="4">
+        <v>1</v>
+      </c>
+      <c r="F233" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -16095,7 +16797,10 @@
       <c r="D234" s="4">
         <v>1</v>
       </c>
-      <c r="E234" s="6" t="inlineStr">
+      <c r="E234" s="4">
+        <v>1</v>
+      </c>
+      <c r="F234" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16158,7 +16863,10 @@
       <c r="D235" s="4">
         <v>1</v>
       </c>
-      <c r="E235" s="6" t="inlineStr">
+      <c r="E235" s="4">
+        <v>1</v>
+      </c>
+      <c r="F235" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -16186,7 +16894,10 @@
       <c r="D236" s="4">
         <v>1</v>
       </c>
-      <c r="E236" s="6" t="inlineStr">
+      <c r="E236" s="4">
+        <v>1</v>
+      </c>
+      <c r="F236" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -16212,9 +16923,12 @@
         </is>
       </c>
       <c r="D237" s="4">
+        <v>3</v>
+      </c>
+      <c r="E237" s="4">
         <v>1</v>
       </c>
-      <c r="E237" s="6" t="inlineStr">
+      <c r="F237" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16292,7 +17006,10 @@
       <c r="D238" s="4">
         <v>1</v>
       </c>
-      <c r="E238" s="6" t="inlineStr">
+      <c r="E238" s="4">
+        <v>1</v>
+      </c>
+      <c r="F238" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -16320,7 +17037,10 @@
       <c r="D239" s="4">
         <v>1</v>
       </c>
-      <c r="E239" s="6" t="inlineStr">
+      <c r="E239" s="4">
+        <v>1</v>
+      </c>
+      <c r="F239" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -16346,9 +17066,12 @@
         </is>
       </c>
       <c r="D240" s="4">
+        <v>3</v>
+      </c>
+      <c r="E240" s="4">
         <v>1</v>
       </c>
-      <c r="E240" s="6" t="inlineStr">
+      <c r="F240" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16402,9 +17125,12 @@
         </is>
       </c>
       <c r="D241" s="4">
+        <v>3</v>
+      </c>
+      <c r="E241" s="4">
         <v>2</v>
       </c>
-      <c r="E241" s="6" t="inlineStr">
+      <c r="F241" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16458,9 +17184,12 @@
         </is>
       </c>
       <c r="D242" s="4">
+        <v>2</v>
+      </c>
+      <c r="E242" s="4">
         <v>1</v>
       </c>
-      <c r="E242" s="6" t="inlineStr">
+      <c r="F242" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16516,7 +17245,10 @@
       <c r="D243" s="4">
         <v>2</v>
       </c>
-      <c r="E243" s="6" t="inlineStr">
+      <c r="E243" s="4">
+        <v>2</v>
+      </c>
+      <c r="F243" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16570,9 +17302,12 @@
         </is>
       </c>
       <c r="D244" s="4">
+        <v>9</v>
+      </c>
+      <c r="E244" s="4">
         <v>1</v>
       </c>
-      <c r="E244" s="6" t="inlineStr">
+      <c r="F244" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16633,9 +17368,12 @@
         </is>
       </c>
       <c r="D245" s="4">
+        <v>9</v>
+      </c>
+      <c r="E245" s="4">
         <v>2</v>
       </c>
-      <c r="E245" s="6" t="inlineStr">
+      <c r="F245" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16696,9 +17434,12 @@
         </is>
       </c>
       <c r="D246" s="4">
+        <v>9</v>
+      </c>
+      <c r="E246" s="4">
         <v>3</v>
       </c>
-      <c r="E246" s="6" t="inlineStr">
+      <c r="F246" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16759,9 +17500,12 @@
         </is>
       </c>
       <c r="D247" s="4">
+        <v>9</v>
+      </c>
+      <c r="E247" s="4">
         <v>4</v>
       </c>
-      <c r="E247" s="6" t="inlineStr">
+      <c r="F247" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16822,9 +17566,12 @@
         </is>
       </c>
       <c r="D248" s="4">
+        <v>9</v>
+      </c>
+      <c r="E248" s="4">
         <v>5</v>
       </c>
-      <c r="E248" s="6" t="inlineStr">
+      <c r="F248" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16885,9 +17632,12 @@
         </is>
       </c>
       <c r="D249" s="4">
+        <v>6</v>
+      </c>
+      <c r="E249" s="4">
         <v>1</v>
       </c>
-      <c r="E249" s="6" t="inlineStr">
+      <c r="F249" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16948,9 +17698,12 @@
         </is>
       </c>
       <c r="D250" s="4">
+        <v>6</v>
+      </c>
+      <c r="E250" s="4">
         <v>2</v>
       </c>
-      <c r="E250" s="6" t="inlineStr">
+      <c r="F250" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17011,9 +17764,12 @@
         </is>
       </c>
       <c r="D251" s="4">
+        <v>9</v>
+      </c>
+      <c r="E251" s="4">
         <v>1</v>
       </c>
-      <c r="E251" s="6" t="inlineStr">
+      <c r="F251" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17074,9 +17830,12 @@
         </is>
       </c>
       <c r="D252" s="4">
+        <v>9</v>
+      </c>
+      <c r="E252" s="4">
         <v>2</v>
       </c>
-      <c r="E252" s="6" t="inlineStr">
+      <c r="F252" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17137,9 +17896,12 @@
         </is>
       </c>
       <c r="D253" s="4">
+        <v>9</v>
+      </c>
+      <c r="E253" s="4">
         <v>3</v>
       </c>
-      <c r="E253" s="6" t="inlineStr">
+      <c r="F253" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17200,9 +17962,12 @@
         </is>
       </c>
       <c r="D254" s="4">
+        <v>9</v>
+      </c>
+      <c r="E254" s="4">
         <v>4</v>
       </c>
-      <c r="E254" s="6" t="inlineStr">
+      <c r="F254" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17263,9 +18028,12 @@
         </is>
       </c>
       <c r="D255" s="4">
+        <v>6</v>
+      </c>
+      <c r="E255" s="4">
         <v>1</v>
       </c>
-      <c r="E255" s="6" t="inlineStr">
+      <c r="F255" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17334,9 +18102,12 @@
         </is>
       </c>
       <c r="D256" s="4">
+        <v>6</v>
+      </c>
+      <c r="E256" s="4">
         <v>2</v>
       </c>
-      <c r="E256" s="6" t="inlineStr">
+      <c r="F256" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17405,9 +18176,12 @@
         </is>
       </c>
       <c r="D257" s="4">
+        <v>6</v>
+      </c>
+      <c r="E257" s="4">
         <v>3</v>
       </c>
-      <c r="E257" s="6" t="inlineStr">
+      <c r="F257" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17476,9 +18250,12 @@
         </is>
       </c>
       <c r="D258" s="4">
+        <v>6</v>
+      </c>
+      <c r="E258" s="4">
         <v>4</v>
       </c>
-      <c r="E258" s="6" t="inlineStr">
+      <c r="F258" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17547,9 +18324,12 @@
         </is>
       </c>
       <c r="D259" s="4">
+        <v>4</v>
+      </c>
+      <c r="E259" s="4">
         <v>1</v>
       </c>
-      <c r="E259" s="6" t="inlineStr">
+      <c r="F259" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17618,9 +18398,12 @@
         </is>
       </c>
       <c r="D260" s="4">
+        <v>4</v>
+      </c>
+      <c r="E260" s="4">
         <v>1</v>
       </c>
-      <c r="E260" s="6" t="inlineStr">
+      <c r="F260" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17689,9 +18472,12 @@
         </is>
       </c>
       <c r="D261" s="4">
+        <v>2</v>
+      </c>
+      <c r="E261" s="4">
         <v>1</v>
       </c>
-      <c r="E261" s="6" t="inlineStr">
+      <c r="F261" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -17717,9 +18503,12 @@
         </is>
       </c>
       <c r="D262" s="4">
+        <v>2</v>
+      </c>
+      <c r="E262" s="4">
         <v>1</v>
       </c>
-      <c r="E262" s="6" t="inlineStr">
+      <c r="F262" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17795,9 +18584,12 @@
         </is>
       </c>
       <c r="D263" s="4">
+        <v>4</v>
+      </c>
+      <c r="E263" s="4">
         <v>1</v>
       </c>
-      <c r="E263" s="6" t="inlineStr">
+      <c r="F263" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17873,9 +18665,12 @@
         </is>
       </c>
       <c r="D264" s="4">
+        <v>4</v>
+      </c>
+      <c r="E264" s="4">
         <v>2</v>
       </c>
-      <c r="E264" s="6" t="inlineStr">
+      <c r="F264" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17951,9 +18746,12 @@
         </is>
       </c>
       <c r="D265" s="4">
+        <v>4</v>
+      </c>
+      <c r="E265" s="4">
         <v>3</v>
       </c>
-      <c r="E265" s="6" t="inlineStr">
+      <c r="F265" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18029,9 +18827,12 @@
         </is>
       </c>
       <c r="D266" s="4">
+        <v>4</v>
+      </c>
+      <c r="E266" s="4">
         <v>1</v>
       </c>
-      <c r="E266" s="6" t="inlineStr">
+      <c r="F266" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18115,9 +18916,12 @@
         </is>
       </c>
       <c r="D267" s="4">
+        <v>4</v>
+      </c>
+      <c r="E267" s="4">
         <v>1</v>
       </c>
-      <c r="E267" s="6" t="inlineStr">
+      <c r="F267" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18201,9 +19005,12 @@
         </is>
       </c>
       <c r="D268" s="4">
+        <v>4</v>
+      </c>
+      <c r="E268" s="4">
         <v>2</v>
       </c>
-      <c r="E268" s="6" t="inlineStr">
+      <c r="F268" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18287,9 +19094,12 @@
         </is>
       </c>
       <c r="D269" s="4">
+        <v>4</v>
+      </c>
+      <c r="E269" s="4">
         <v>3</v>
       </c>
-      <c r="E269" s="6" t="inlineStr">
+      <c r="F269" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18373,9 +19183,12 @@
         </is>
       </c>
       <c r="D270" s="4">
+        <v>4</v>
+      </c>
+      <c r="E270" s="4">
         <v>1</v>
       </c>
-      <c r="E270" s="6" t="inlineStr">
+      <c r="F270" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18466,9 +19279,12 @@
         </is>
       </c>
       <c r="D271" s="4">
+        <v>4</v>
+      </c>
+      <c r="E271" s="4">
         <v>2</v>
       </c>
-      <c r="E271" s="6" t="inlineStr">
+      <c r="F271" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18559,9 +19375,12 @@
         </is>
       </c>
       <c r="D272" s="4">
+        <v>4</v>
+      </c>
+      <c r="E272" s="4">
         <v>3</v>
       </c>
-      <c r="E272" s="6" t="inlineStr">
+      <c r="F272" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18652,9 +19471,12 @@
         </is>
       </c>
       <c r="D273" s="4">
+        <v>2</v>
+      </c>
+      <c r="E273" s="4">
         <v>1</v>
       </c>
-      <c r="E273" s="6" t="inlineStr">
+      <c r="F273" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -18680,9 +19502,12 @@
         </is>
       </c>
       <c r="D274" s="4">
+        <v>7</v>
+      </c>
+      <c r="E274" s="4">
         <v>1</v>
       </c>
-      <c r="E274" s="6" t="inlineStr">
+      <c r="F274" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18773,9 +19598,12 @@
         </is>
       </c>
       <c r="D275" s="4">
+        <v>7</v>
+      </c>
+      <c r="E275" s="4">
         <v>2</v>
       </c>
-      <c r="E275" s="6" t="inlineStr">
+      <c r="F275" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18866,9 +19694,12 @@
         </is>
       </c>
       <c r="D276" s="4">
+        <v>7</v>
+      </c>
+      <c r="E276" s="4">
         <v>3</v>
       </c>
-      <c r="E276" s="6" t="inlineStr">
+      <c r="F276" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18959,9 +19790,12 @@
         </is>
       </c>
       <c r="D277" s="4">
+        <v>7</v>
+      </c>
+      <c r="E277" s="4">
         <v>4</v>
       </c>
-      <c r="E277" s="6" t="inlineStr">
+      <c r="F277" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19052,9 +19886,12 @@
         </is>
       </c>
       <c r="D278" s="4">
+        <v>7</v>
+      </c>
+      <c r="E278" s="4">
         <v>5</v>
       </c>
-      <c r="E278" s="6" t="inlineStr">
+      <c r="F278" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19145,9 +19982,12 @@
         </is>
       </c>
       <c r="D279" s="4">
+        <v>3</v>
+      </c>
+      <c r="E279" s="4">
         <v>1</v>
       </c>
-      <c r="E279" s="6" t="inlineStr">
+      <c r="F279" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19246,9 +20086,12 @@
         </is>
       </c>
       <c r="D280" s="4">
+        <v>3</v>
+      </c>
+      <c r="E280" s="4">
         <v>2</v>
       </c>
-      <c r="E280" s="6" t="inlineStr">
+      <c r="F280" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19347,9 +20190,12 @@
         </is>
       </c>
       <c r="D281" s="4">
+        <v>6</v>
+      </c>
+      <c r="E281" s="4">
         <v>1</v>
       </c>
-      <c r="E281" s="6" t="inlineStr">
+      <c r="F281" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19448,9 +20294,12 @@
         </is>
       </c>
       <c r="D282" s="4">
+        <v>6</v>
+      </c>
+      <c r="E282" s="4">
         <v>2</v>
       </c>
-      <c r="E282" s="6" t="inlineStr">
+      <c r="F282" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19549,9 +20398,12 @@
         </is>
       </c>
       <c r="D283" s="4">
+        <v>6</v>
+      </c>
+      <c r="E283" s="4">
         <v>3</v>
       </c>
-      <c r="E283" s="6" t="inlineStr">
+      <c r="F283" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19650,9 +20502,12 @@
         </is>
       </c>
       <c r="D284" s="4">
+        <v>12</v>
+      </c>
+      <c r="E284" s="4">
         <v>1</v>
       </c>
-      <c r="E284" s="6" t="inlineStr">
+      <c r="F284" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19751,9 +20606,12 @@
         </is>
       </c>
       <c r="D285" s="4">
+        <v>12</v>
+      </c>
+      <c r="E285" s="4">
         <v>2</v>
       </c>
-      <c r="E285" s="6" t="inlineStr">
+      <c r="F285" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19852,9 +20710,12 @@
         </is>
       </c>
       <c r="D286" s="4">
+        <v>12</v>
+      </c>
+      <c r="E286" s="4">
         <v>3</v>
       </c>
-      <c r="E286" s="6" t="inlineStr">
+      <c r="F286" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19953,9 +20814,12 @@
         </is>
       </c>
       <c r="D287" s="4">
+        <v>12</v>
+      </c>
+      <c r="E287" s="4">
         <v>4</v>
       </c>
-      <c r="E287" s="6" t="inlineStr">
+      <c r="F287" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20054,9 +20918,12 @@
         </is>
       </c>
       <c r="D288" s="4">
+        <v>12</v>
+      </c>
+      <c r="E288" s="4">
         <v>5</v>
       </c>
-      <c r="E288" s="6" t="inlineStr">
+      <c r="F288" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20155,9 +21022,12 @@
         </is>
       </c>
       <c r="D289" s="4">
+        <v>8</v>
+      </c>
+      <c r="E289" s="4">
         <v>1</v>
       </c>
-      <c r="E289" s="6" t="inlineStr">
+      <c r="F289" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20263,9 +21133,12 @@
         </is>
       </c>
       <c r="D290" s="4">
+        <v>7</v>
+      </c>
+      <c r="E290" s="4">
         <v>1</v>
       </c>
-      <c r="E290" s="6" t="inlineStr">
+      <c r="F290" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20371,9 +21244,12 @@
         </is>
       </c>
       <c r="D291" s="4">
+        <v>7</v>
+      </c>
+      <c r="E291" s="4">
         <v>2</v>
       </c>
-      <c r="E291" s="6" t="inlineStr">
+      <c r="F291" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20479,9 +21355,12 @@
         </is>
       </c>
       <c r="D292" s="4">
+        <v>5</v>
+      </c>
+      <c r="E292" s="4">
         <v>1</v>
       </c>
-      <c r="E292" s="6" t="inlineStr">
+      <c r="F292" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20587,9 +21466,12 @@
         </is>
       </c>
       <c r="D293" s="4">
+        <v>5</v>
+      </c>
+      <c r="E293" s="4">
         <v>2</v>
       </c>
-      <c r="E293" s="6" t="inlineStr">
+      <c r="F293" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20695,9 +21577,12 @@
         </is>
       </c>
       <c r="D294" s="4">
+        <v>6</v>
+      </c>
+      <c r="E294" s="4">
         <v>1</v>
       </c>
-      <c r="E294" s="6" t="inlineStr">
+      <c r="F294" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -20723,9 +21608,12 @@
         </is>
       </c>
       <c r="D295" s="4">
+        <v>5</v>
+      </c>
+      <c r="E295" s="4">
         <v>1</v>
       </c>
-      <c r="E295" s="6" t="inlineStr">
+      <c r="F295" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20839,9 +21727,12 @@
         </is>
       </c>
       <c r="D296" s="4">
+        <v>7</v>
+      </c>
+      <c r="E296" s="4">
         <v>1</v>
       </c>
-      <c r="E296" s="6" t="inlineStr">
+      <c r="F296" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20955,9 +21846,12 @@
         </is>
       </c>
       <c r="D297" s="4">
+        <v>7</v>
+      </c>
+      <c r="E297" s="4">
         <v>2</v>
       </c>
-      <c r="E297" s="6" t="inlineStr">
+      <c r="F297" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21071,9 +21965,12 @@
         </is>
       </c>
       <c r="D298" s="4">
+        <v>7</v>
+      </c>
+      <c r="E298" s="4">
         <v>3</v>
       </c>
-      <c r="E298" s="6" t="inlineStr">
+      <c r="F298" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21187,9 +22084,12 @@
         </is>
       </c>
       <c r="D299" s="4">
+        <v>7</v>
+      </c>
+      <c r="E299" s="4">
         <v>4</v>
       </c>
-      <c r="E299" s="6" t="inlineStr">
+      <c r="F299" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21303,9 +22203,12 @@
         </is>
       </c>
       <c r="D300" s="4">
+        <v>7</v>
+      </c>
+      <c r="E300" s="4">
         <v>1</v>
       </c>
-      <c r="E300" s="6" t="inlineStr">
+      <c r="F300" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21426,9 +22329,12 @@
         </is>
       </c>
       <c r="D301" s="4">
+        <v>7</v>
+      </c>
+      <c r="E301" s="4">
         <v>2</v>
       </c>
-      <c r="E301" s="6" t="inlineStr">
+      <c r="F301" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21549,9 +22455,12 @@
         </is>
       </c>
       <c r="D302" s="4">
+        <v>8</v>
+      </c>
+      <c r="E302" s="4">
         <v>1</v>
       </c>
-      <c r="E302" s="6" t="inlineStr">
+      <c r="F302" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21672,9 +22581,12 @@
         </is>
       </c>
       <c r="D303" s="4">
+        <v>8</v>
+      </c>
+      <c r="E303" s="4">
         <v>2</v>
       </c>
-      <c r="E303" s="6" t="inlineStr">
+      <c r="F303" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21795,9 +22707,12 @@
         </is>
       </c>
       <c r="D304" s="4">
+        <v>8</v>
+      </c>
+      <c r="E304" s="4">
         <v>3</v>
       </c>
-      <c r="E304" s="6" t="inlineStr">
+      <c r="F304" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21918,9 +22833,12 @@
         </is>
       </c>
       <c r="D305" s="4">
+        <v>8</v>
+      </c>
+      <c r="E305" s="4">
         <v>4</v>
       </c>
-      <c r="E305" s="6" t="inlineStr">
+      <c r="F305" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22041,9 +22959,12 @@
         </is>
       </c>
       <c r="D306" s="4">
+        <v>8</v>
+      </c>
+      <c r="E306" s="4">
         <v>5</v>
       </c>
-      <c r="E306" s="6" t="inlineStr">
+      <c r="F306" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22164,9 +23085,12 @@
         </is>
       </c>
       <c r="D307" s="4">
+        <v>4</v>
+      </c>
+      <c r="E307" s="4">
         <v>1</v>
       </c>
-      <c r="E307" s="6" t="inlineStr">
+      <c r="F307" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22287,9 +23211,12 @@
         </is>
       </c>
       <c r="D308" s="4">
+        <v>4</v>
+      </c>
+      <c r="E308" s="4">
         <v>2</v>
       </c>
-      <c r="E308" s="6" t="inlineStr">
+      <c r="F308" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22410,9 +23337,12 @@
         </is>
       </c>
       <c r="D309" s="4">
+        <v>2</v>
+      </c>
+      <c r="E309" s="4">
         <v>1</v>
       </c>
-      <c r="E309" s="6" t="inlineStr">
+      <c r="F309" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22468,7 +23398,10 @@
       <c r="D310" s="4">
         <v>1</v>
       </c>
-      <c r="E310" s="6" t="inlineStr">
+      <c r="E310" s="4">
+        <v>1</v>
+      </c>
+      <c r="F310" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -22496,7 +23429,10 @@
       <c r="D311" s="4">
         <v>1</v>
       </c>
-      <c r="E311" s="6" t="inlineStr">
+      <c r="E311" s="4">
+        <v>1</v>
+      </c>
+      <c r="F311" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22550,9 +23486,12 @@
         </is>
       </c>
       <c r="D312" s="4">
+        <v>3</v>
+      </c>
+      <c r="E312" s="4">
         <v>1</v>
       </c>
-      <c r="E312" s="6" t="inlineStr">
+      <c r="F312" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -22578,9 +23517,12 @@
         </is>
       </c>
       <c r="D313" s="4">
+        <v>2</v>
+      </c>
+      <c r="E313" s="4">
         <v>1</v>
       </c>
-      <c r="E313" s="6" t="inlineStr">
+      <c r="F313" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22643,7 +23585,10 @@
       <c r="D314" s="4">
         <v>2</v>
       </c>
-      <c r="E314" s="6" t="inlineStr">
+      <c r="E314" s="4">
+        <v>2</v>
+      </c>
+      <c r="F314" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22704,9 +23649,12 @@
         </is>
       </c>
       <c r="D315" s="4">
+        <v>2</v>
+      </c>
+      <c r="E315" s="4">
         <v>1</v>
       </c>
-      <c r="E315" s="6" t="inlineStr">
+      <c r="F315" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22777,7 +23725,10 @@
       <c r="D316" s="4">
         <v>1</v>
       </c>
-      <c r="E316" s="6" t="inlineStr">
+      <c r="E316" s="4">
+        <v>1</v>
+      </c>
+      <c r="F316" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -22805,7 +23756,10 @@
       <c r="D317" s="4">
         <v>1</v>
       </c>
-      <c r="E317" s="6" t="inlineStr">
+      <c r="E317" s="4">
+        <v>1</v>
+      </c>
+      <c r="F317" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22883,7 +23837,10 @@
       <c r="D318" s="4">
         <v>1</v>
       </c>
-      <c r="E318" s="6" t="inlineStr">
+      <c r="E318" s="4">
+        <v>1</v>
+      </c>
+      <c r="F318" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22969,7 +23926,10 @@
       <c r="D319" s="4">
         <v>1</v>
       </c>
-      <c r="E319" s="6" t="inlineStr">
+      <c r="E319" s="4">
+        <v>1</v>
+      </c>
+      <c r="F319" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23060,9 +24020,12 @@
         </is>
       </c>
       <c r="D320" s="4">
+        <v>2</v>
+      </c>
+      <c r="E320" s="4">
         <v>1</v>
       </c>
-      <c r="E320" s="6" t="inlineStr">
+      <c r="F320" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23153,9 +24116,12 @@
         </is>
       </c>
       <c r="D321" s="4">
+        <v>2</v>
+      </c>
+      <c r="E321" s="4">
         <v>1</v>
       </c>
-      <c r="E321" s="6" t="inlineStr">
+      <c r="F321" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -23181,9 +24147,12 @@
         </is>
       </c>
       <c r="D322" s="4">
+        <v>8</v>
+      </c>
+      <c r="E322" s="4">
         <v>1</v>
       </c>
-      <c r="E322" s="6" t="inlineStr">
+      <c r="F322" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23282,9 +24251,12 @@
         </is>
       </c>
       <c r="D323" s="4">
+        <v>8</v>
+      </c>
+      <c r="E323" s="4">
         <v>2</v>
       </c>
-      <c r="E323" s="6" t="inlineStr">
+      <c r="F323" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23383,9 +24355,12 @@
         </is>
       </c>
       <c r="D324" s="4">
+        <v>8</v>
+      </c>
+      <c r="E324" s="4">
         <v>3</v>
       </c>
-      <c r="E324" s="6" t="inlineStr">
+      <c r="F324" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23484,9 +24459,12 @@
         </is>
       </c>
       <c r="D325" s="4">
+        <v>8</v>
+      </c>
+      <c r="E325" s="4">
         <v>4</v>
       </c>
-      <c r="E325" s="6" t="inlineStr">
+      <c r="F325" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23585,9 +24563,12 @@
         </is>
       </c>
       <c r="D326" s="4">
+        <v>4</v>
+      </c>
+      <c r="E326" s="4">
         <v>1</v>
       </c>
-      <c r="E326" s="6" t="inlineStr">
+      <c r="F326" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23686,9 +24667,12 @@
         </is>
       </c>
       <c r="D327" s="4">
+        <v>4</v>
+      </c>
+      <c r="E327" s="4">
         <v>2</v>
       </c>
-      <c r="E327" s="6" t="inlineStr">
+      <c r="F327" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23787,9 +24771,12 @@
         </is>
       </c>
       <c r="D328" s="4">
+        <v>4</v>
+      </c>
+      <c r="E328" s="4">
         <v>1</v>
       </c>
-      <c r="E328" s="6" t="inlineStr">
+      <c r="F328" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23895,9 +24882,12 @@
         </is>
       </c>
       <c r="D329" s="4">
+        <v>8</v>
+      </c>
+      <c r="E329" s="4">
         <v>1</v>
       </c>
-      <c r="E329" s="6" t="inlineStr">
+      <c r="F329" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24003,9 +24993,12 @@
         </is>
       </c>
       <c r="D330" s="4">
+        <v>8</v>
+      </c>
+      <c r="E330" s="4">
         <v>2</v>
       </c>
-      <c r="E330" s="6" t="inlineStr">
+      <c r="F330" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24111,9 +25104,12 @@
         </is>
       </c>
       <c r="D331" s="4">
+        <v>8</v>
+      </c>
+      <c r="E331" s="4">
         <v>3</v>
       </c>
-      <c r="E331" s="6" t="inlineStr">
+      <c r="F331" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24219,9 +25215,12 @@
         </is>
       </c>
       <c r="D332" s="4">
+        <v>8</v>
+      </c>
+      <c r="E332" s="4">
         <v>4</v>
       </c>
-      <c r="E332" s="6" t="inlineStr">
+      <c r="F332" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24327,9 +25326,12 @@
         </is>
       </c>
       <c r="D333" s="4">
+        <v>3</v>
+      </c>
+      <c r="E333" s="4">
         <v>1</v>
       </c>
-      <c r="E333" s="6" t="inlineStr">
+      <c r="F333" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24443,9 +25445,12 @@
         </is>
       </c>
       <c r="D334" s="4">
+        <v>3</v>
+      </c>
+      <c r="E334" s="4">
         <v>2</v>
       </c>
-      <c r="E334" s="6" t="inlineStr">
+      <c r="F334" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24559,9 +25564,12 @@
         </is>
       </c>
       <c r="D335" s="4">
+        <v>2</v>
+      </c>
+      <c r="E335" s="4">
         <v>1</v>
       </c>
-      <c r="E335" s="6" t="inlineStr">
+      <c r="F335" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24675,9 +25683,12 @@
         </is>
       </c>
       <c r="D336" s="4">
+        <v>3</v>
+      </c>
+      <c r="E336" s="4">
         <v>1</v>
       </c>
-      <c r="E336" s="6" t="inlineStr">
+      <c r="F336" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24791,9 +25802,12 @@
         </is>
       </c>
       <c r="D337" s="4">
+        <v>2</v>
+      </c>
+      <c r="E337" s="4">
         <v>1</v>
       </c>
-      <c r="E337" s="6" t="inlineStr">
+      <c r="F337" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24916,7 +25930,10 @@
       <c r="D338" s="4">
         <v>2</v>
       </c>
-      <c r="E338" s="6" t="inlineStr">
+      <c r="E338" s="4">
+        <v>2</v>
+      </c>
+      <c r="F338" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25037,9 +26054,12 @@
         </is>
       </c>
       <c r="D339" s="4">
+        <v>3</v>
+      </c>
+      <c r="E339" s="4">
         <v>1</v>
       </c>
-      <c r="E339" s="6" t="inlineStr">
+      <c r="F339" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25160,9 +26180,12 @@
         </is>
       </c>
       <c r="D340" s="4">
+        <v>3</v>
+      </c>
+      <c r="E340" s="4">
         <v>2</v>
       </c>
-      <c r="E340" s="6" t="inlineStr">
+      <c r="F340" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25283,9 +26306,12 @@
         </is>
       </c>
       <c r="D341" s="4">
+        <v>3</v>
+      </c>
+      <c r="E341" s="4">
         <v>1</v>
       </c>
-      <c r="E341" s="6" t="inlineStr">
+      <c r="F341" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25406,9 +26432,12 @@
         </is>
       </c>
       <c r="D342" s="4">
+        <v>2</v>
+      </c>
+      <c r="E342" s="4">
         <v>1</v>
       </c>
-      <c r="E342" s="6" t="inlineStr">
+      <c r="F342" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25462,9 +26491,12 @@
         </is>
       </c>
       <c r="D343" s="4">
+        <v>3</v>
+      </c>
+      <c r="E343" s="4">
         <v>1</v>
       </c>
-      <c r="E343" s="6" t="inlineStr">
+      <c r="F343" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25525,9 +26557,12 @@
         </is>
       </c>
       <c r="D344" s="4">
+        <v>3</v>
+      </c>
+      <c r="E344" s="4">
         <v>2</v>
       </c>
-      <c r="E344" s="6" t="inlineStr">
+      <c r="F344" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25588,9 +26623,12 @@
         </is>
       </c>
       <c r="D345" s="4">
+        <v>2</v>
+      </c>
+      <c r="E345" s="4">
         <v>1</v>
       </c>
-      <c r="E345" s="6" t="inlineStr">
+      <c r="F345" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25653,7 +26691,10 @@
       <c r="D346" s="4">
         <v>1</v>
       </c>
-      <c r="E346" s="6" t="inlineStr">
+      <c r="E346" s="4">
+        <v>1</v>
+      </c>
+      <c r="F346" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -25679,9 +26720,12 @@
         </is>
       </c>
       <c r="D347" s="4">
+        <v>2</v>
+      </c>
+      <c r="E347" s="4">
         <v>1</v>
       </c>
-      <c r="E347" s="6" t="inlineStr">
+      <c r="F347" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -25709,7 +26753,10 @@
       <c r="D348" s="4">
         <v>1</v>
       </c>
-      <c r="E348" s="6" t="inlineStr">
+      <c r="E348" s="4">
+        <v>1</v>
+      </c>
+      <c r="F348" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -25737,7 +26784,10 @@
       <c r="D349" s="4">
         <v>1</v>
       </c>
-      <c r="E349" s="6" t="inlineStr">
+      <c r="E349" s="4">
+        <v>1</v>
+      </c>
+      <c r="F349" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -25763,9 +26813,12 @@
         </is>
       </c>
       <c r="D350" s="4">
+        <v>5</v>
+      </c>
+      <c r="E350" s="4">
         <v>1</v>
       </c>
-      <c r="E350" s="6" t="inlineStr">
+      <c r="F350" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25864,9 +26917,12 @@
         </is>
       </c>
       <c r="D351" s="4">
+        <v>5</v>
+      </c>
+      <c r="E351" s="4">
         <v>2</v>
       </c>
-      <c r="E351" s="6" t="inlineStr">
+      <c r="F351" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25967,7 +27023,10 @@
       <c r="D352" s="4">
         <v>1</v>
       </c>
-      <c r="E352" s="6" t="inlineStr">
+      <c r="E352" s="4">
+        <v>1</v>
+      </c>
+      <c r="F352" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -25995,7 +27054,10 @@
       <c r="D353" s="4">
         <v>1</v>
       </c>
-      <c r="E353" s="6" t="inlineStr">
+      <c r="E353" s="4">
+        <v>1</v>
+      </c>
+      <c r="F353" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -26021,9 +27083,12 @@
         </is>
       </c>
       <c r="D354" s="4">
+        <v>2</v>
+      </c>
+      <c r="E354" s="4">
         <v>1</v>
       </c>
-      <c r="E354" s="6" t="inlineStr">
+      <c r="F354" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26129,9 +27194,12 @@
         </is>
       </c>
       <c r="D355" s="4">
+        <v>3</v>
+      </c>
+      <c r="E355" s="4">
         <v>1</v>
       </c>
-      <c r="E355" s="6" t="inlineStr">
+      <c r="F355" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -26157,9 +27225,12 @@
         </is>
       </c>
       <c r="D356" s="4">
+        <v>6</v>
+      </c>
+      <c r="E356" s="4">
         <v>1</v>
       </c>
-      <c r="E356" s="6" t="inlineStr">
+      <c r="F356" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26265,9 +27336,12 @@
         </is>
       </c>
       <c r="D357" s="4">
+        <v>6</v>
+      </c>
+      <c r="E357" s="4">
         <v>2</v>
       </c>
-      <c r="E357" s="6" t="inlineStr">
+      <c r="F357" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26373,9 +27447,12 @@
         </is>
       </c>
       <c r="D358" s="4">
+        <v>6</v>
+      </c>
+      <c r="E358" s="4">
         <v>3</v>
       </c>
-      <c r="E358" s="6" t="inlineStr">
+      <c r="F358" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26481,9 +27558,12 @@
         </is>
       </c>
       <c r="D359" s="4">
+        <v>6</v>
+      </c>
+      <c r="E359" s="4">
         <v>4</v>
       </c>
-      <c r="E359" s="6" t="inlineStr">
+      <c r="F359" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26589,9 +27669,12 @@
         </is>
       </c>
       <c r="D360" s="4">
+        <v>6</v>
+      </c>
+      <c r="E360" s="4">
         <v>1</v>
       </c>
-      <c r="E360" s="6" t="inlineStr">
+      <c r="F360" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26705,9 +27788,12 @@
         </is>
       </c>
       <c r="D361" s="4">
+        <v>6</v>
+      </c>
+      <c r="E361" s="4">
         <v>2</v>
       </c>
-      <c r="E361" s="6" t="inlineStr">
+      <c r="F361" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26821,9 +27907,12 @@
         </is>
       </c>
       <c r="D362" s="4">
+        <v>3</v>
+      </c>
+      <c r="E362" s="4">
         <v>1</v>
       </c>
-      <c r="E362" s="6" t="inlineStr">
+      <c r="F362" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26937,9 +28026,12 @@
         </is>
       </c>
       <c r="D363" s="4">
+        <v>3</v>
+      </c>
+      <c r="E363" s="4">
         <v>1</v>
       </c>
-      <c r="E363" s="6" t="inlineStr">
+      <c r="F363" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27053,9 +28145,12 @@
         </is>
       </c>
       <c r="D364" s="4">
+        <v>2</v>
+      </c>
+      <c r="E364" s="4">
         <v>1</v>
       </c>
-      <c r="E364" s="6" t="inlineStr">
+      <c r="F364" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27178,7 +28273,10 @@
       <c r="D365" s="4">
         <v>1</v>
       </c>
-      <c r="E365" s="6" t="inlineStr">
+      <c r="E365" s="4">
+        <v>1</v>
+      </c>
+      <c r="F365" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -27204,9 +28302,12 @@
         </is>
       </c>
       <c r="D366" s="4">
+        <v>3</v>
+      </c>
+      <c r="E366" s="4">
         <v>1</v>
       </c>
-      <c r="E366" s="6" t="inlineStr">
+      <c r="F366" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27260,9 +28361,12 @@
         </is>
       </c>
       <c r="D367" s="4">
+        <v>3</v>
+      </c>
+      <c r="E367" s="4">
         <v>2</v>
       </c>
-      <c r="E367" s="6" t="inlineStr">
+      <c r="F367" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27318,7 +28422,10 @@
       <c r="D368" s="4">
         <v>3</v>
       </c>
-      <c r="E368" s="6" t="inlineStr">
+      <c r="E368" s="4">
+        <v>3</v>
+      </c>
+      <c r="F368" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27374,7 +28481,10 @@
       <c r="D369" s="4">
         <v>1</v>
       </c>
-      <c r="E369" s="6" t="inlineStr">
+      <c r="E369" s="4">
+        <v>1</v>
+      </c>
+      <c r="F369" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27430,7 +28540,10 @@
       <c r="D370" s="4">
         <v>1</v>
       </c>
-      <c r="E370" s="6" t="inlineStr">
+      <c r="E370" s="4">
+        <v>1</v>
+      </c>
+      <c r="F370" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27484,9 +28597,12 @@
         </is>
       </c>
       <c r="D371" s="4">
+        <v>9</v>
+      </c>
+      <c r="E371" s="4">
         <v>1</v>
       </c>
-      <c r="E371" s="6" t="inlineStr">
+      <c r="F371" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27540,9 +28656,12 @@
         </is>
       </c>
       <c r="D372" s="4">
+        <v>9</v>
+      </c>
+      <c r="E372" s="4">
         <v>2</v>
       </c>
-      <c r="E372" s="6" t="inlineStr">
+      <c r="F372" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27596,9 +28715,12 @@
         </is>
       </c>
       <c r="D373" s="4">
+        <v>9</v>
+      </c>
+      <c r="E373" s="4">
         <v>3</v>
       </c>
-      <c r="E373" s="6" t="inlineStr">
+      <c r="F373" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27652,9 +28774,12 @@
         </is>
       </c>
       <c r="D374" s="4">
+        <v>9</v>
+      </c>
+      <c r="E374" s="4">
         <v>4</v>
       </c>
-      <c r="E374" s="6" t="inlineStr">
+      <c r="F374" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27708,9 +28833,12 @@
         </is>
       </c>
       <c r="D375" s="4">
+        <v>9</v>
+      </c>
+      <c r="E375" s="4">
         <v>5</v>
       </c>
-      <c r="E375" s="6" t="inlineStr">
+      <c r="F375" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27764,9 +28892,12 @@
         </is>
       </c>
       <c r="D376" s="4">
+        <v>9</v>
+      </c>
+      <c r="E376" s="4">
         <v>6</v>
       </c>
-      <c r="E376" s="6" t="inlineStr">
+      <c r="F376" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27820,9 +28951,12 @@
         </is>
       </c>
       <c r="D377" s="4">
+        <v>9</v>
+      </c>
+      <c r="E377" s="4">
         <v>7</v>
       </c>
-      <c r="E377" s="6" t="inlineStr">
+      <c r="F377" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27876,9 +29010,12 @@
         </is>
       </c>
       <c r="D378" s="4">
+        <v>9</v>
+      </c>
+      <c r="E378" s="4">
         <v>8</v>
       </c>
-      <c r="E378" s="6" t="inlineStr">
+      <c r="F378" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27934,7 +29071,10 @@
       <c r="D379" s="4">
         <v>9</v>
       </c>
-      <c r="E379" s="6" t="inlineStr">
+      <c r="E379" s="4">
+        <v>9</v>
+      </c>
+      <c r="F379" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27988,9 +29128,12 @@
         </is>
       </c>
       <c r="D380" s="4">
+        <v>6</v>
+      </c>
+      <c r="E380" s="4">
         <v>1</v>
       </c>
-      <c r="E380" s="6" t="inlineStr">
+      <c r="F380" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28044,9 +29187,12 @@
         </is>
       </c>
       <c r="D381" s="4">
+        <v>6</v>
+      </c>
+      <c r="E381" s="4">
         <v>2</v>
       </c>
-      <c r="E381" s="6" t="inlineStr">
+      <c r="F381" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28100,9 +29246,12 @@
         </is>
       </c>
       <c r="D382" s="4">
+        <v>6</v>
+      </c>
+      <c r="E382" s="4">
         <v>3</v>
       </c>
-      <c r="E382" s="6" t="inlineStr">
+      <c r="F382" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28156,9 +29305,12 @@
         </is>
       </c>
       <c r="D383" s="4">
+        <v>6</v>
+      </c>
+      <c r="E383" s="4">
         <v>4</v>
       </c>
-      <c r="E383" s="6" t="inlineStr">
+      <c r="F383" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28212,9 +29364,12 @@
         </is>
       </c>
       <c r="D384" s="4">
+        <v>6</v>
+      </c>
+      <c r="E384" s="4">
         <v>5</v>
       </c>
-      <c r="E384" s="6" t="inlineStr">
+      <c r="F384" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28270,7 +29425,10 @@
       <c r="D385" s="4">
         <v>6</v>
       </c>
-      <c r="E385" s="6" t="inlineStr">
+      <c r="E385" s="4">
+        <v>6</v>
+      </c>
+      <c r="F385" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28324,9 +29482,12 @@
         </is>
       </c>
       <c r="D386" s="4">
+        <v>2</v>
+      </c>
+      <c r="E386" s="4">
         <v>1</v>
       </c>
-      <c r="E386" s="6" t="inlineStr">
+      <c r="F386" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28382,7 +29543,10 @@
       <c r="D387" s="4">
         <v>2</v>
       </c>
-      <c r="E387" s="6" t="inlineStr">
+      <c r="E387" s="4">
+        <v>2</v>
+      </c>
+      <c r="F387" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28436,9 +29600,12 @@
         </is>
       </c>
       <c r="D388" s="4">
+        <v>6</v>
+      </c>
+      <c r="E388" s="4">
         <v>1</v>
       </c>
-      <c r="E388" s="6" t="inlineStr">
+      <c r="F388" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28492,9 +29659,12 @@
         </is>
       </c>
       <c r="D389" s="4">
+        <v>6</v>
+      </c>
+      <c r="E389" s="4">
         <v>2</v>
       </c>
-      <c r="E389" s="6" t="inlineStr">
+      <c r="F389" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28548,9 +29718,12 @@
         </is>
       </c>
       <c r="D390" s="4">
+        <v>6</v>
+      </c>
+      <c r="E390" s="4">
         <v>3</v>
       </c>
-      <c r="E390" s="6" t="inlineStr">
+      <c r="F390" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28604,9 +29777,12 @@
         </is>
       </c>
       <c r="D391" s="4">
+        <v>6</v>
+      </c>
+      <c r="E391" s="4">
         <v>4</v>
       </c>
-      <c r="E391" s="6" t="inlineStr">
+      <c r="F391" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28660,9 +29836,12 @@
         </is>
       </c>
       <c r="D392" s="4">
+        <v>6</v>
+      </c>
+      <c r="E392" s="4">
         <v>5</v>
       </c>
-      <c r="E392" s="6" t="inlineStr">
+      <c r="F392" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28718,7 +29897,10 @@
       <c r="D393" s="4">
         <v>6</v>
       </c>
-      <c r="E393" s="6" t="inlineStr">
+      <c r="E393" s="4">
+        <v>6</v>
+      </c>
+      <c r="F393" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28772,9 +29954,12 @@
         </is>
       </c>
       <c r="D394" s="4">
+        <v>3</v>
+      </c>
+      <c r="E394" s="4">
         <v>1</v>
       </c>
-      <c r="E394" s="6" t="inlineStr">
+      <c r="F394" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28828,9 +30013,12 @@
         </is>
       </c>
       <c r="D395" s="4">
+        <v>3</v>
+      </c>
+      <c r="E395" s="4">
         <v>2</v>
       </c>
-      <c r="E395" s="6" t="inlineStr">
+      <c r="F395" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28886,7 +30074,10 @@
       <c r="D396" s="4">
         <v>3</v>
       </c>
-      <c r="E396" s="6" t="inlineStr">
+      <c r="E396" s="4">
+        <v>3</v>
+      </c>
+      <c r="F396" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28940,9 +30131,12 @@
         </is>
       </c>
       <c r="D397" s="4">
+        <v>3</v>
+      </c>
+      <c r="E397" s="4">
         <v>1</v>
       </c>
-      <c r="E397" s="6" t="inlineStr">
+      <c r="F397" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28996,9 +30190,12 @@
         </is>
       </c>
       <c r="D398" s="4">
+        <v>3</v>
+      </c>
+      <c r="E398" s="4">
         <v>2</v>
       </c>
-      <c r="E398" s="6" t="inlineStr">
+      <c r="F398" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29052,9 +30249,12 @@
         </is>
       </c>
       <c r="D399" s="4">
+        <v>4</v>
+      </c>
+      <c r="E399" s="4">
         <v>1</v>
       </c>
-      <c r="E399" s="6" t="inlineStr">
+      <c r="F399" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29108,9 +30308,12 @@
         </is>
       </c>
       <c r="D400" s="4">
+        <v>4</v>
+      </c>
+      <c r="E400" s="4">
         <v>2</v>
       </c>
-      <c r="E400" s="6" t="inlineStr">
+      <c r="F400" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29164,9 +30367,12 @@
         </is>
       </c>
       <c r="D401" s="4">
+        <v>4</v>
+      </c>
+      <c r="E401" s="4">
         <v>3</v>
       </c>
-      <c r="E401" s="6" t="inlineStr">
+      <c r="F401" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29220,9 +30426,12 @@
         </is>
       </c>
       <c r="D402" s="4">
+        <v>23</v>
+      </c>
+      <c r="E402" s="4">
         <v>1</v>
       </c>
-      <c r="E402" s="6" t="inlineStr">
+      <c r="F402" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29276,9 +30485,12 @@
         </is>
       </c>
       <c r="D403" s="4">
+        <v>23</v>
+      </c>
+      <c r="E403" s="4">
         <v>2</v>
       </c>
-      <c r="E403" s="6" t="inlineStr">
+      <c r="F403" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29332,9 +30544,12 @@
         </is>
       </c>
       <c r="D404" s="4">
+        <v>23</v>
+      </c>
+      <c r="E404" s="4">
         <v>3</v>
       </c>
-      <c r="E404" s="6" t="inlineStr">
+      <c r="F404" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29388,9 +30603,12 @@
         </is>
       </c>
       <c r="D405" s="4">
+        <v>23</v>
+      </c>
+      <c r="E405" s="4">
         <v>4</v>
       </c>
-      <c r="E405" s="6" t="inlineStr">
+      <c r="F405" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29444,9 +30662,12 @@
         </is>
       </c>
       <c r="D406" s="4">
+        <v>23</v>
+      </c>
+      <c r="E406" s="4">
         <v>5</v>
       </c>
-      <c r="E406" s="6" t="inlineStr">
+      <c r="F406" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29500,9 +30721,12 @@
         </is>
       </c>
       <c r="D407" s="4">
+        <v>23</v>
+      </c>
+      <c r="E407" s="4">
         <v>6</v>
       </c>
-      <c r="E407" s="6" t="inlineStr">
+      <c r="F407" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29556,9 +30780,12 @@
         </is>
       </c>
       <c r="D408" s="4">
+        <v>23</v>
+      </c>
+      <c r="E408" s="4">
         <v>7</v>
       </c>
-      <c r="E408" s="6" t="inlineStr">
+      <c r="F408" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29612,9 +30839,12 @@
         </is>
       </c>
       <c r="D409" s="4">
+        <v>23</v>
+      </c>
+      <c r="E409" s="4">
         <v>8</v>
       </c>
-      <c r="E409" s="6" t="inlineStr">
+      <c r="F409" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29668,9 +30898,12 @@
         </is>
       </c>
       <c r="D410" s="4">
+        <v>23</v>
+      </c>
+      <c r="E410" s="4">
         <v>9</v>
       </c>
-      <c r="E410" s="6" t="inlineStr">
+      <c r="F410" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29724,9 +30957,12 @@
         </is>
       </c>
       <c r="D411" s="4">
+        <v>23</v>
+      </c>
+      <c r="E411" s="4">
         <v>10</v>
       </c>
-      <c r="E411" s="6" t="inlineStr">
+      <c r="F411" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29780,9 +31016,12 @@
         </is>
       </c>
       <c r="D412" s="4">
+        <v>23</v>
+      </c>
+      <c r="E412" s="4">
         <v>11</v>
       </c>
-      <c r="E412" s="6" t="inlineStr">
+      <c r="F412" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29836,9 +31075,12 @@
         </is>
       </c>
       <c r="D413" s="4">
+        <v>23</v>
+      </c>
+      <c r="E413" s="4">
         <v>12</v>
       </c>
-      <c r="E413" s="6" t="inlineStr">
+      <c r="F413" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29892,9 +31134,12 @@
         </is>
       </c>
       <c r="D414" s="4">
+        <v>23</v>
+      </c>
+      <c r="E414" s="4">
         <v>13</v>
       </c>
-      <c r="E414" s="6" t="inlineStr">
+      <c r="F414" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29948,9 +31193,12 @@
         </is>
       </c>
       <c r="D415" s="4">
+        <v>23</v>
+      </c>
+      <c r="E415" s="4">
         <v>14</v>
       </c>
-      <c r="E415" s="6" t="inlineStr">
+      <c r="F415" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30004,9 +31252,12 @@
         </is>
       </c>
       <c r="D416" s="4">
+        <v>23</v>
+      </c>
+      <c r="E416" s="4">
         <v>15</v>
       </c>
-      <c r="E416" s="6" t="inlineStr">
+      <c r="F416" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30060,9 +31311,12 @@
         </is>
       </c>
       <c r="D417" s="4">
+        <v>23</v>
+      </c>
+      <c r="E417" s="4">
         <v>16</v>
       </c>
-      <c r="E417" s="6" t="inlineStr">
+      <c r="F417" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30116,9 +31370,12 @@
         </is>
       </c>
       <c r="D418" s="4">
+        <v>23</v>
+      </c>
+      <c r="E418" s="4">
         <v>17</v>
       </c>
-      <c r="E418" s="6" t="inlineStr">
+      <c r="F418" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30172,9 +31429,12 @@
         </is>
       </c>
       <c r="D419" s="4">
+        <v>23</v>
+      </c>
+      <c r="E419" s="4">
         <v>18</v>
       </c>
-      <c r="E419" s="6" t="inlineStr">
+      <c r="F419" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30228,9 +31488,12 @@
         </is>
       </c>
       <c r="D420" s="4">
+        <v>23</v>
+      </c>
+      <c r="E420" s="4">
         <v>19</v>
       </c>
-      <c r="E420" s="6" t="inlineStr">
+      <c r="F420" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30284,9 +31547,12 @@
         </is>
       </c>
       <c r="D421" s="4">
+        <v>23</v>
+      </c>
+      <c r="E421" s="4">
         <v>20</v>
       </c>
-      <c r="E421" s="6" t="inlineStr">
+      <c r="F421" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30340,9 +31606,12 @@
         </is>
       </c>
       <c r="D422" s="4">
+        <v>3</v>
+      </c>
+      <c r="E422" s="4">
         <v>1</v>
       </c>
-      <c r="E422" s="6" t="inlineStr">
+      <c r="F422" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30412,9 +31681,12 @@
         </is>
       </c>
       <c r="D423" s="4">
+        <v>3</v>
+      </c>
+      <c r="E423" s="4">
         <v>2</v>
       </c>
-      <c r="E423" s="6" t="inlineStr">
+      <c r="F423" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30486,7 +31758,10 @@
       <c r="D424" s="4">
         <v>3</v>
       </c>
-      <c r="E424" s="6" t="inlineStr">
+      <c r="E424" s="4">
+        <v>3</v>
+      </c>
+      <c r="F424" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30558,7 +31833,10 @@
       <c r="D425" s="4">
         <v>1</v>
       </c>
-      <c r="E425" s="6" t="inlineStr">
+      <c r="E425" s="4">
+        <v>1</v>
+      </c>
+      <c r="F425" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30621,7 +31899,10 @@
       <c r="D426" s="4">
         <v>1</v>
       </c>
-      <c r="E426" s="6" t="inlineStr">
+      <c r="E426" s="4">
+        <v>1</v>
+      </c>
+      <c r="F426" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30690,9 +31971,12 @@
         </is>
       </c>
       <c r="D427" s="4">
+        <v>13</v>
+      </c>
+      <c r="E427" s="4">
         <v>1</v>
       </c>
-      <c r="E427" s="6" t="inlineStr">
+      <c r="F427" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30753,9 +32037,12 @@
         </is>
       </c>
       <c r="D428" s="4">
+        <v>13</v>
+      </c>
+      <c r="E428" s="4">
         <v>2</v>
       </c>
-      <c r="E428" s="6" t="inlineStr">
+      <c r="F428" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30816,9 +32103,12 @@
         </is>
       </c>
       <c r="D429" s="4">
+        <v>13</v>
+      </c>
+      <c r="E429" s="4">
         <v>3</v>
       </c>
-      <c r="E429" s="6" t="inlineStr">
+      <c r="F429" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30879,9 +32169,12 @@
         </is>
       </c>
       <c r="D430" s="4">
+        <v>13</v>
+      </c>
+      <c r="E430" s="4">
         <v>4</v>
       </c>
-      <c r="E430" s="6" t="inlineStr">
+      <c r="F430" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30942,9 +32235,12 @@
         </is>
       </c>
       <c r="D431" s="4">
+        <v>13</v>
+      </c>
+      <c r="E431" s="4">
         <v>5</v>
       </c>
-      <c r="E431" s="6" t="inlineStr">
+      <c r="F431" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31005,9 +32301,12 @@
         </is>
       </c>
       <c r="D432" s="4">
+        <v>13</v>
+      </c>
+      <c r="E432" s="4">
         <v>6</v>
       </c>
-      <c r="E432" s="6" t="inlineStr">
+      <c r="F432" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31068,9 +32367,12 @@
         </is>
       </c>
       <c r="D433" s="4">
+        <v>13</v>
+      </c>
+      <c r="E433" s="4">
         <v>7</v>
       </c>
-      <c r="E433" s="6" t="inlineStr">
+      <c r="F433" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31131,9 +32433,12 @@
         </is>
       </c>
       <c r="D434" s="4">
+        <v>13</v>
+      </c>
+      <c r="E434" s="4">
         <v>8</v>
       </c>
-      <c r="E434" s="6" t="inlineStr">
+      <c r="F434" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31194,9 +32499,12 @@
         </is>
       </c>
       <c r="D435" s="4">
+        <v>13</v>
+      </c>
+      <c r="E435" s="4">
         <v>9</v>
       </c>
-      <c r="E435" s="6" t="inlineStr">
+      <c r="F435" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31257,9 +32565,12 @@
         </is>
       </c>
       <c r="D436" s="4">
+        <v>13</v>
+      </c>
+      <c r="E436" s="4">
         <v>10</v>
       </c>
-      <c r="E436" s="6" t="inlineStr">
+      <c r="F436" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31320,9 +32631,12 @@
         </is>
       </c>
       <c r="D437" s="4">
+        <v>13</v>
+      </c>
+      <c r="E437" s="4">
         <v>11</v>
       </c>
-      <c r="E437" s="6" t="inlineStr">
+      <c r="F437" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31383,9 +32697,12 @@
         </is>
       </c>
       <c r="D438" s="4">
+        <v>13</v>
+      </c>
+      <c r="E438" s="4">
         <v>12</v>
       </c>
-      <c r="E438" s="6" t="inlineStr">
+      <c r="F438" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31448,7 +32765,10 @@
       <c r="D439" s="4">
         <v>13</v>
       </c>
-      <c r="E439" s="6" t="inlineStr">
+      <c r="E439" s="4">
+        <v>13</v>
+      </c>
+      <c r="F439" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31509,9 +32829,12 @@
         </is>
       </c>
       <c r="D440" s="4">
+        <v>4</v>
+      </c>
+      <c r="E440" s="4">
         <v>1</v>
       </c>
-      <c r="E440" s="6" t="inlineStr">
+      <c r="F440" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31580,9 +32903,12 @@
         </is>
       </c>
       <c r="D441" s="4">
+        <v>4</v>
+      </c>
+      <c r="E441" s="4">
         <v>2</v>
       </c>
-      <c r="E441" s="6" t="inlineStr">
+      <c r="F441" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31651,9 +32977,12 @@
         </is>
       </c>
       <c r="D442" s="4">
+        <v>4</v>
+      </c>
+      <c r="E442" s="4">
         <v>3</v>
       </c>
-      <c r="E442" s="6" t="inlineStr">
+      <c r="F442" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31724,7 +33053,10 @@
       <c r="D443" s="4">
         <v>4</v>
       </c>
-      <c r="E443" s="6" t="inlineStr">
+      <c r="E443" s="4">
+        <v>4</v>
+      </c>
+      <c r="F443" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31795,7 +33127,10 @@
       <c r="D444" s="4">
         <v>1</v>
       </c>
-      <c r="E444" s="6" t="inlineStr">
+      <c r="E444" s="4">
+        <v>1</v>
+      </c>
+      <c r="F444" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31873,7 +33208,10 @@
       <c r="D445" s="4">
         <v>1</v>
       </c>
-      <c r="E445" s="6" t="inlineStr">
+      <c r="E445" s="4">
+        <v>1</v>
+      </c>
+      <c r="F445" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31943,9 +33281,12 @@
         </is>
       </c>
       <c r="D446" s="4">
+        <v>4</v>
+      </c>
+      <c r="E446" s="4">
         <v>1</v>
       </c>
-      <c r="E446" s="6" t="inlineStr">
+      <c r="F446" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32006,9 +33347,12 @@
         </is>
       </c>
       <c r="D447" s="4">
+        <v>4</v>
+      </c>
+      <c r="E447" s="4">
         <v>2</v>
       </c>
-      <c r="E447" s="6" t="inlineStr">
+      <c r="F447" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32069,9 +33413,12 @@
         </is>
       </c>
       <c r="D448" s="4">
+        <v>4</v>
+      </c>
+      <c r="E448" s="4">
         <v>3</v>
       </c>
-      <c r="E448" s="6" t="inlineStr">
+      <c r="F448" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32134,7 +33481,10 @@
       <c r="D449" s="4">
         <v>4</v>
       </c>
-      <c r="E449" s="6" t="inlineStr">
+      <c r="E449" s="4">
+        <v>4</v>
+      </c>
+      <c r="F449" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32197,7 +33547,10 @@
       <c r="D450" s="4">
         <v>1</v>
       </c>
-      <c r="E450" s="6" t="inlineStr">
+      <c r="E450" s="4">
+        <v>1</v>
+      </c>
+      <c r="F450" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32268,7 +33621,10 @@
       <c r="D451" s="4">
         <v>1</v>
       </c>
-      <c r="E451" s="6" t="inlineStr">
+      <c r="E451" s="4">
+        <v>1</v>
+      </c>
+      <c r="F451" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32346,7 +33702,10 @@
       <c r="D452" s="4">
         <v>1</v>
       </c>
-      <c r="E452" s="6" t="inlineStr">
+      <c r="E452" s="4">
+        <v>1</v>
+      </c>
+      <c r="F452" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32415,9 +33774,12 @@
         </is>
       </c>
       <c r="D453" s="4">
+        <v>8</v>
+      </c>
+      <c r="E453" s="4">
         <v>1</v>
       </c>
-      <c r="E453" s="6" t="inlineStr">
+      <c r="F453" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32478,9 +33840,12 @@
         </is>
       </c>
       <c r="D454" s="4">
+        <v>8</v>
+      </c>
+      <c r="E454" s="4">
         <v>2</v>
       </c>
-      <c r="E454" s="6" t="inlineStr">
+      <c r="F454" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32541,9 +33906,12 @@
         </is>
       </c>
       <c r="D455" s="4">
+        <v>8</v>
+      </c>
+      <c r="E455" s="4">
         <v>3</v>
       </c>
-      <c r="E455" s="6" t="inlineStr">
+      <c r="F455" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32604,9 +33972,12 @@
         </is>
       </c>
       <c r="D456" s="4">
+        <v>8</v>
+      </c>
+      <c r="E456" s="4">
         <v>4</v>
       </c>
-      <c r="E456" s="6" t="inlineStr">
+      <c r="F456" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32667,9 +34038,12 @@
         </is>
       </c>
       <c r="D457" s="4">
+        <v>8</v>
+      </c>
+      <c r="E457" s="4">
         <v>5</v>
       </c>
-      <c r="E457" s="6" t="inlineStr">
+      <c r="F457" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32730,9 +34104,12 @@
         </is>
       </c>
       <c r="D458" s="4">
+        <v>8</v>
+      </c>
+      <c r="E458" s="4">
         <v>6</v>
       </c>
-      <c r="E458" s="6" t="inlineStr">
+      <c r="F458" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32793,9 +34170,12 @@
         </is>
       </c>
       <c r="D459" s="4">
+        <v>8</v>
+      </c>
+      <c r="E459" s="4">
         <v>7</v>
       </c>
-      <c r="E459" s="6" t="inlineStr">
+      <c r="F459" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32858,7 +34238,10 @@
       <c r="D460" s="4">
         <v>1</v>
       </c>
-      <c r="E460" s="6" t="inlineStr">
+      <c r="E460" s="4">
+        <v>1</v>
+      </c>
+      <c r="F460" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32929,7 +34312,10 @@
       <c r="D461" s="4">
         <v>1</v>
       </c>
-      <c r="E461" s="6" t="inlineStr">
+      <c r="E461" s="4">
+        <v>1</v>
+      </c>
+      <c r="F461" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33015,7 +34401,10 @@
       <c r="D462" s="4">
         <v>1</v>
       </c>
-      <c r="E462" s="6" t="inlineStr">
+      <c r="E462" s="4">
+        <v>1</v>
+      </c>
+      <c r="F462" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33087,7 +34476,10 @@
       <c r="D463" s="4">
         <v>1</v>
       </c>
-      <c r="E463" s="6" t="inlineStr">
+      <c r="E463" s="4">
+        <v>1</v>
+      </c>
+      <c r="F463" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33148,9 +34540,12 @@
         </is>
       </c>
       <c r="D464" s="4">
+        <v>3</v>
+      </c>
+      <c r="E464" s="4">
         <v>1</v>
       </c>
-      <c r="E464" s="6" t="inlineStr">
+      <c r="F464" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33220,9 +34615,12 @@
         </is>
       </c>
       <c r="D465" s="4">
+        <v>3</v>
+      </c>
+      <c r="E465" s="4">
         <v>2</v>
       </c>
-      <c r="E465" s="6" t="inlineStr">
+      <c r="F465" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33294,7 +34692,10 @@
       <c r="D466" s="4">
         <v>3</v>
       </c>
-      <c r="E466" s="6" t="inlineStr">
+      <c r="E466" s="4">
+        <v>3</v>
+      </c>
+      <c r="F466" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33364,9 +34765,12 @@
         </is>
       </c>
       <c r="D467" s="4">
+        <v>2</v>
+      </c>
+      <c r="E467" s="4">
         <v>1</v>
       </c>
-      <c r="E467" s="6" t="inlineStr">
+      <c r="F467" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33438,7 +34842,10 @@
       <c r="D468" s="4">
         <v>2</v>
       </c>
-      <c r="E468" s="6" t="inlineStr">
+      <c r="E468" s="4">
+        <v>2</v>
+      </c>
+      <c r="F468" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33508,9 +34915,12 @@
         </is>
       </c>
       <c r="D469" s="4">
+        <v>3</v>
+      </c>
+      <c r="E469" s="4">
         <v>1</v>
       </c>
-      <c r="E469" s="6" t="inlineStr">
+      <c r="F469" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33564,9 +34974,12 @@
         </is>
       </c>
       <c r="D470" s="4">
+        <v>3</v>
+      </c>
+      <c r="E470" s="4">
         <v>2</v>
       </c>
-      <c r="E470" s="6" t="inlineStr">
+      <c r="F470" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33622,7 +35035,10 @@
       <c r="D471" s="4">
         <v>3</v>
       </c>
-      <c r="E471" s="6" t="inlineStr">
+      <c r="E471" s="4">
+        <v>3</v>
+      </c>
+      <c r="F471" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33678,7 +35094,10 @@
       <c r="D472" s="4">
         <v>1</v>
       </c>
-      <c r="E472" s="6" t="inlineStr">
+      <c r="E472" s="4">
+        <v>1</v>
+      </c>
+      <c r="F472" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33734,7 +35153,10 @@
       <c r="D473" s="4">
         <v>1</v>
       </c>
-      <c r="E473" s="6" t="inlineStr">
+      <c r="E473" s="4">
+        <v>1</v>
+      </c>
+      <c r="F473" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33797,7 +35219,10 @@
       <c r="D474" s="4">
         <v>1</v>
       </c>
-      <c r="E474" s="6" t="inlineStr">
+      <c r="E474" s="4">
+        <v>1</v>
+      </c>
+      <c r="F474" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33866,9 +35291,12 @@
         </is>
       </c>
       <c r="D475" s="4">
+        <v>2</v>
+      </c>
+      <c r="E475" s="4">
         <v>1</v>
       </c>
-      <c r="E475" s="6" t="inlineStr">
+      <c r="F475" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33931,7 +35359,10 @@
       <c r="D476" s="4">
         <v>2</v>
       </c>
-      <c r="E476" s="6" t="inlineStr">
+      <c r="E476" s="4">
+        <v>2</v>
+      </c>
+      <c r="F476" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33992,9 +35423,12 @@
         </is>
       </c>
       <c r="D477" s="4">
+        <v>2</v>
+      </c>
+      <c r="E477" s="4">
         <v>1</v>
       </c>
-      <c r="E477" s="6" t="inlineStr">
+      <c r="F477" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34065,7 +35499,10 @@
       <c r="D478" s="4">
         <v>2</v>
       </c>
-      <c r="E478" s="6" t="inlineStr">
+      <c r="E478" s="4">
+        <v>2</v>
+      </c>
+      <c r="F478" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34134,9 +35571,12 @@
         </is>
       </c>
       <c r="D479" s="4">
+        <v>2</v>
+      </c>
+      <c r="E479" s="4">
         <v>1</v>
       </c>
-      <c r="E479" s="6" t="inlineStr">
+      <c r="F479" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34244,7 +35684,10 @@
       <c r="D480" s="4">
         <v>2</v>
       </c>
-      <c r="E480" s="6" t="inlineStr">
+      <c r="E480" s="4">
+        <v>2</v>
+      </c>
+      <c r="F480" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34352,7 +35795,10 @@
       <c r="D481" s="4">
         <v>1</v>
       </c>
-      <c r="E481" s="6" t="inlineStr">
+      <c r="E481" s="4">
+        <v>1</v>
+      </c>
+      <c r="F481" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34415,7 +35861,10 @@
       <c r="D482" s="4">
         <v>1</v>
       </c>
-      <c r="E482" s="6" t="inlineStr">
+      <c r="E482" s="4">
+        <v>1</v>
+      </c>
+      <c r="F482" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34493,7 +35942,10 @@
       <c r="D483" s="4">
         <v>1</v>
       </c>
-      <c r="E483" s="6" t="inlineStr">
+      <c r="E483" s="4">
+        <v>1</v>
+      </c>
+      <c r="F483" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34554,9 +36006,12 @@
         </is>
       </c>
       <c r="D484" s="4">
+        <v>2</v>
+      </c>
+      <c r="E484" s="4">
         <v>1</v>
       </c>
-      <c r="E484" s="6" t="inlineStr">
+      <c r="F484" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34642,7 +36097,10 @@
       <c r="D485" s="4">
         <v>2</v>
       </c>
-      <c r="E485" s="6" t="inlineStr">
+      <c r="E485" s="4">
+        <v>2</v>
+      </c>
+      <c r="F485" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34728,7 +36186,10 @@
       <c r="D486" s="4">
         <v>1</v>
       </c>
-      <c r="E486" s="6" t="inlineStr">
+      <c r="E486" s="4">
+        <v>1</v>
+      </c>
+      <c r="F486" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34834,9 +36295,12 @@
         </is>
       </c>
       <c r="D487" s="4">
+        <v>14</v>
+      </c>
+      <c r="E487" s="4">
         <v>1</v>
       </c>
-      <c r="E487" s="6" t="inlineStr">
+      <c r="F487" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34897,9 +36361,12 @@
         </is>
       </c>
       <c r="D488" s="4">
+        <v>14</v>
+      </c>
+      <c r="E488" s="4">
         <v>2</v>
       </c>
-      <c r="E488" s="6" t="inlineStr">
+      <c r="F488" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34960,9 +36427,12 @@
         </is>
       </c>
       <c r="D489" s="4">
+        <v>14</v>
+      </c>
+      <c r="E489" s="4">
         <v>3</v>
       </c>
-      <c r="E489" s="6" t="inlineStr">
+      <c r="F489" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35023,9 +36493,12 @@
         </is>
       </c>
       <c r="D490" s="4">
+        <v>14</v>
+      </c>
+      <c r="E490" s="4">
         <v>4</v>
       </c>
-      <c r="E490" s="6" t="inlineStr">
+      <c r="F490" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35086,9 +36559,12 @@
         </is>
       </c>
       <c r="D491" s="4">
+        <v>14</v>
+      </c>
+      <c r="E491" s="4">
         <v>5</v>
       </c>
-      <c r="E491" s="6" t="inlineStr">
+      <c r="F491" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35149,9 +36625,12 @@
         </is>
       </c>
       <c r="D492" s="4">
+        <v>14</v>
+      </c>
+      <c r="E492" s="4">
         <v>6</v>
       </c>
-      <c r="E492" s="6" t="inlineStr">
+      <c r="F492" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35212,9 +36691,12 @@
         </is>
       </c>
       <c r="D493" s="4">
+        <v>14</v>
+      </c>
+      <c r="E493" s="4">
         <v>7</v>
       </c>
-      <c r="E493" s="6" t="inlineStr">
+      <c r="F493" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35275,9 +36757,12 @@
         </is>
       </c>
       <c r="D494" s="4">
+        <v>14</v>
+      </c>
+      <c r="E494" s="4">
         <v>8</v>
       </c>
-      <c r="E494" s="6" t="inlineStr">
+      <c r="F494" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35338,9 +36823,12 @@
         </is>
       </c>
       <c r="D495" s="4">
+        <v>14</v>
+      </c>
+      <c r="E495" s="4">
         <v>9</v>
       </c>
-      <c r="E495" s="6" t="inlineStr">
+      <c r="F495" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35401,9 +36889,12 @@
         </is>
       </c>
       <c r="D496" s="4">
+        <v>14</v>
+      </c>
+      <c r="E496" s="4">
         <v>10</v>
       </c>
-      <c r="E496" s="6" t="inlineStr">
+      <c r="F496" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35464,9 +36955,12 @@
         </is>
       </c>
       <c r="D497" s="4">
+        <v>14</v>
+      </c>
+      <c r="E497" s="4">
         <v>11</v>
       </c>
-      <c r="E497" s="6" t="inlineStr">
+      <c r="F497" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35527,9 +37021,12 @@
         </is>
       </c>
       <c r="D498" s="4">
+        <v>14</v>
+      </c>
+      <c r="E498" s="4">
         <v>12</v>
       </c>
-      <c r="E498" s="6" t="inlineStr">
+      <c r="F498" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35590,9 +37087,12 @@
         </is>
       </c>
       <c r="D499" s="4">
+        <v>14</v>
+      </c>
+      <c r="E499" s="4">
         <v>13</v>
       </c>
-      <c r="E499" s="6" t="inlineStr">
+      <c r="F499" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35653,9 +37153,12 @@
         </is>
       </c>
       <c r="D500" s="4">
+        <v>9</v>
+      </c>
+      <c r="E500" s="4">
         <v>1</v>
       </c>
-      <c r="E500" s="6" t="inlineStr">
+      <c r="F500" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35725,9 +37228,12 @@
         </is>
       </c>
       <c r="D501" s="4">
+        <v>9</v>
+      </c>
+      <c r="E501" s="4">
         <v>2</v>
       </c>
-      <c r="E501" s="6" t="inlineStr">
+      <c r="F501" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35797,9 +37303,12 @@
         </is>
       </c>
       <c r="D502" s="4">
+        <v>9</v>
+      </c>
+      <c r="E502" s="4">
         <v>3</v>
       </c>
-      <c r="E502" s="6" t="inlineStr">
+      <c r="F502" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35869,9 +37378,12 @@
         </is>
       </c>
       <c r="D503" s="4">
+        <v>9</v>
+      </c>
+      <c r="E503" s="4">
         <v>4</v>
       </c>
-      <c r="E503" s="6" t="inlineStr">
+      <c r="F503" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35941,9 +37453,12 @@
         </is>
       </c>
       <c r="D504" s="4">
+        <v>9</v>
+      </c>
+      <c r="E504" s="4">
         <v>5</v>
       </c>
-      <c r="E504" s="6" t="inlineStr">
+      <c r="F504" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36013,9 +37528,12 @@
         </is>
       </c>
       <c r="D505" s="4">
+        <v>9</v>
+      </c>
+      <c r="E505" s="4">
         <v>6</v>
       </c>
-      <c r="E505" s="6" t="inlineStr">
+      <c r="F505" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36085,9 +37603,12 @@
         </is>
       </c>
       <c r="D506" s="4">
+        <v>9</v>
+      </c>
+      <c r="E506" s="4">
         <v>7</v>
       </c>
-      <c r="E506" s="6" t="inlineStr">
+      <c r="F506" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36157,9 +37678,12 @@
         </is>
       </c>
       <c r="D507" s="4">
+        <v>9</v>
+      </c>
+      <c r="E507" s="4">
         <v>8</v>
       </c>
-      <c r="E507" s="6" t="inlineStr">
+      <c r="F507" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36229,9 +37753,12 @@
         </is>
       </c>
       <c r="D508" s="4">
+        <v>6</v>
+      </c>
+      <c r="E508" s="4">
         <v>1</v>
       </c>
-      <c r="E508" s="6" t="inlineStr">
+      <c r="F508" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36301,9 +37828,12 @@
         </is>
       </c>
       <c r="D509" s="4">
+        <v>6</v>
+      </c>
+      <c r="E509" s="4">
         <v>2</v>
       </c>
-      <c r="E509" s="6" t="inlineStr">
+      <c r="F509" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36373,9 +37903,12 @@
         </is>
       </c>
       <c r="D510" s="4">
+        <v>6</v>
+      </c>
+      <c r="E510" s="4">
         <v>3</v>
       </c>
-      <c r="E510" s="6" t="inlineStr">
+      <c r="F510" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36445,9 +37978,12 @@
         </is>
       </c>
       <c r="D511" s="4">
+        <v>6</v>
+      </c>
+      <c r="E511" s="4">
         <v>4</v>
       </c>
-      <c r="E511" s="6" t="inlineStr">
+      <c r="F511" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36517,9 +38053,12 @@
         </is>
       </c>
       <c r="D512" s="4">
+        <v>6</v>
+      </c>
+      <c r="E512" s="4">
         <v>5</v>
       </c>
-      <c r="E512" s="6" t="inlineStr">
+      <c r="F512" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36591,7 +38130,10 @@
       <c r="D513" s="4">
         <v>6</v>
       </c>
-      <c r="E513" s="6" t="inlineStr">
+      <c r="E513" s="4">
+        <v>6</v>
+      </c>
+      <c r="F513" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36661,9 +38203,12 @@
         </is>
       </c>
       <c r="D514" s="4">
+        <v>5</v>
+      </c>
+      <c r="E514" s="4">
         <v>1</v>
       </c>
-      <c r="E514" s="6" t="inlineStr">
+      <c r="F514" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36733,9 +38278,12 @@
         </is>
       </c>
       <c r="D515" s="4">
+        <v>5</v>
+      </c>
+      <c r="E515" s="4">
         <v>2</v>
       </c>
-      <c r="E515" s="6" t="inlineStr">
+      <c r="F515" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36805,9 +38353,12 @@
         </is>
       </c>
       <c r="D516" s="4">
+        <v>5</v>
+      </c>
+      <c r="E516" s="4">
         <v>3</v>
       </c>
-      <c r="E516" s="6" t="inlineStr">
+      <c r="F516" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36877,9 +38428,12 @@
         </is>
       </c>
       <c r="D517" s="4">
+        <v>5</v>
+      </c>
+      <c r="E517" s="4">
         <v>4</v>
       </c>
-      <c r="E517" s="6" t="inlineStr">
+      <c r="F517" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36951,7 +38505,10 @@
       <c r="D518" s="4">
         <v>5</v>
       </c>
-      <c r="E518" s="6" t="inlineStr">
+      <c r="E518" s="4">
+        <v>5</v>
+      </c>
+      <c r="F518" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37021,9 +38578,12 @@
         </is>
       </c>
       <c r="D519" s="4">
+        <v>6</v>
+      </c>
+      <c r="E519" s="4">
         <v>1</v>
       </c>
-      <c r="E519" s="6" t="inlineStr">
+      <c r="F519" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37093,9 +38653,12 @@
         </is>
       </c>
       <c r="D520" s="4">
+        <v>6</v>
+      </c>
+      <c r="E520" s="4">
         <v>2</v>
       </c>
-      <c r="E520" s="6" t="inlineStr">
+      <c r="F520" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37165,9 +38728,12 @@
         </is>
       </c>
       <c r="D521" s="4">
+        <v>6</v>
+      </c>
+      <c r="E521" s="4">
         <v>3</v>
       </c>
-      <c r="E521" s="6" t="inlineStr">
+      <c r="F521" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37237,9 +38803,12 @@
         </is>
       </c>
       <c r="D522" s="4">
+        <v>6</v>
+      </c>
+      <c r="E522" s="4">
         <v>4</v>
       </c>
-      <c r="E522" s="6" t="inlineStr">
+      <c r="F522" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37309,9 +38878,12 @@
         </is>
       </c>
       <c r="D523" s="4">
+        <v>6</v>
+      </c>
+      <c r="E523" s="4">
         <v>5</v>
       </c>
-      <c r="E523" s="6" t="inlineStr">
+      <c r="F523" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37383,7 +38955,10 @@
       <c r="D524" s="4">
         <v>6</v>
       </c>
-      <c r="E524" s="6" t="inlineStr">
+      <c r="E524" s="4">
+        <v>6</v>
+      </c>
+      <c r="F524" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37453,9 +39028,12 @@
         </is>
       </c>
       <c r="D525" s="4">
+        <v>3</v>
+      </c>
+      <c r="E525" s="4">
         <v>1</v>
       </c>
-      <c r="E525" s="6" t="inlineStr">
+      <c r="F525" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37525,9 +39103,12 @@
         </is>
       </c>
       <c r="D526" s="4">
+        <v>3</v>
+      </c>
+      <c r="E526" s="4">
         <v>2</v>
       </c>
-      <c r="E526" s="6" t="inlineStr">
+      <c r="F526" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37599,7 +39180,10 @@
       <c r="D527" s="4">
         <v>3</v>
       </c>
-      <c r="E527" s="6" t="inlineStr">
+      <c r="E527" s="4">
+        <v>3</v>
+      </c>
+      <c r="F527" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37669,9 +39253,12 @@
         </is>
       </c>
       <c r="D528" s="4">
+        <v>3</v>
+      </c>
+      <c r="E528" s="4">
         <v>1</v>
       </c>
-      <c r="E528" s="6" t="inlineStr">
+      <c r="F528" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37741,9 +39328,12 @@
         </is>
       </c>
       <c r="D529" s="4">
+        <v>3</v>
+      </c>
+      <c r="E529" s="4">
         <v>2</v>
       </c>
-      <c r="E529" s="6" t="inlineStr">
+      <c r="F529" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37815,7 +39405,10 @@
       <c r="D530" s="4">
         <v>3</v>
       </c>
-      <c r="E530" s="6" t="inlineStr">
+      <c r="E530" s="4">
+        <v>3</v>
+      </c>
+      <c r="F530" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37885,9 +39478,12 @@
         </is>
       </c>
       <c r="D531" s="4">
+        <v>3</v>
+      </c>
+      <c r="E531" s="4">
         <v>1</v>
       </c>
-      <c r="E531" s="6" t="inlineStr">
+      <c r="F531" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37957,9 +39553,12 @@
         </is>
       </c>
       <c r="D532" s="4">
+        <v>3</v>
+      </c>
+      <c r="E532" s="4">
         <v>2</v>
       </c>
-      <c r="E532" s="6" t="inlineStr">
+      <c r="F532" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38031,7 +39630,10 @@
       <c r="D533" s="4">
         <v>3</v>
       </c>
-      <c r="E533" s="6" t="inlineStr">
+      <c r="E533" s="4">
+        <v>3</v>
+      </c>
+      <c r="F533" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38101,9 +39703,12 @@
         </is>
       </c>
       <c r="D534" s="4">
+        <v>2</v>
+      </c>
+      <c r="E534" s="4">
         <v>1</v>
       </c>
-      <c r="E534" s="6" t="inlineStr">
+      <c r="F534" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38175,7 +39780,10 @@
       <c r="D535" s="4">
         <v>2</v>
       </c>
-      <c r="E535" s="6" t="inlineStr">
+      <c r="E535" s="4">
+        <v>2</v>
+      </c>
+      <c r="F535" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38247,7 +39855,10 @@
       <c r="D536" s="4">
         <v>1</v>
       </c>
-      <c r="E536" s="6" t="inlineStr">
+      <c r="E536" s="4">
+        <v>1</v>
+      </c>
+      <c r="F536" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38317,9 +39928,12 @@
         </is>
       </c>
       <c r="D537" s="4">
+        <v>2</v>
+      </c>
+      <c r="E537" s="4">
         <v>1</v>
       </c>
-      <c r="E537" s="6" t="inlineStr">
+      <c r="F537" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38391,7 +40005,10 @@
       <c r="D538" s="4">
         <v>2</v>
       </c>
-      <c r="E538" s="6" t="inlineStr">
+      <c r="E538" s="4">
+        <v>2</v>
+      </c>
+      <c r="F538" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38463,7 +40080,10 @@
       <c r="D539" s="4">
         <v>1</v>
       </c>
-      <c r="E539" s="6" t="inlineStr">
+      <c r="E539" s="4">
+        <v>1</v>
+      </c>
+      <c r="F539" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38533,9 +40153,12 @@
         </is>
       </c>
       <c r="D540" s="4">
+        <v>50</v>
+      </c>
+      <c r="E540" s="4">
         <v>1</v>
       </c>
-      <c r="E540" s="6" t="inlineStr">
+      <c r="F540" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38605,9 +40228,12 @@
         </is>
       </c>
       <c r="D541" s="4">
+        <v>50</v>
+      </c>
+      <c r="E541" s="4">
         <v>2</v>
       </c>
-      <c r="E541" s="6" t="inlineStr">
+      <c r="F541" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38677,9 +40303,12 @@
         </is>
       </c>
       <c r="D542" s="4">
+        <v>50</v>
+      </c>
+      <c r="E542" s="4">
         <v>3</v>
       </c>
-      <c r="E542" s="6" t="inlineStr">
+      <c r="F542" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38749,9 +40378,12 @@
         </is>
       </c>
       <c r="D543" s="4">
+        <v>50</v>
+      </c>
+      <c r="E543" s="4">
         <v>4</v>
       </c>
-      <c r="E543" s="6" t="inlineStr">
+      <c r="F543" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38821,9 +40453,12 @@
         </is>
       </c>
       <c r="D544" s="4">
+        <v>50</v>
+      </c>
+      <c r="E544" s="4">
         <v>5</v>
       </c>
-      <c r="E544" s="6" t="inlineStr">
+      <c r="F544" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38893,9 +40528,12 @@
         </is>
       </c>
       <c r="D545" s="4">
+        <v>50</v>
+      </c>
+      <c r="E545" s="4">
         <v>6</v>
       </c>
-      <c r="E545" s="6" t="inlineStr">
+      <c r="F545" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38965,9 +40603,12 @@
         </is>
       </c>
       <c r="D546" s="4">
+        <v>50</v>
+      </c>
+      <c r="E546" s="4">
         <v>7</v>
       </c>
-      <c r="E546" s="6" t="inlineStr">
+      <c r="F546" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39037,9 +40678,12 @@
         </is>
       </c>
       <c r="D547" s="4">
+        <v>50</v>
+      </c>
+      <c r="E547" s="4">
         <v>8</v>
       </c>
-      <c r="E547" s="6" t="inlineStr">
+      <c r="F547" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39109,9 +40753,12 @@
         </is>
       </c>
       <c r="D548" s="4">
+        <v>50</v>
+      </c>
+      <c r="E548" s="4">
         <v>9</v>
       </c>
-      <c r="E548" s="6" t="inlineStr">
+      <c r="F548" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39181,9 +40828,12 @@
         </is>
       </c>
       <c r="D549" s="4">
+        <v>50</v>
+      </c>
+      <c r="E549" s="4">
         <v>10</v>
       </c>
-      <c r="E549" s="6" t="inlineStr">
+      <c r="F549" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39253,9 +40903,12 @@
         </is>
       </c>
       <c r="D550" s="4">
+        <v>50</v>
+      </c>
+      <c r="E550" s="4">
         <v>11</v>
       </c>
-      <c r="E550" s="6" t="inlineStr">
+      <c r="F550" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39325,9 +40978,12 @@
         </is>
       </c>
       <c r="D551" s="4">
+        <v>50</v>
+      </c>
+      <c r="E551" s="4">
         <v>12</v>
       </c>
-      <c r="E551" s="6" t="inlineStr">
+      <c r="F551" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39397,9 +41053,12 @@
         </is>
       </c>
       <c r="D552" s="4">
+        <v>50</v>
+      </c>
+      <c r="E552" s="4">
         <v>13</v>
       </c>
-      <c r="E552" s="6" t="inlineStr">
+      <c r="F552" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39469,9 +41128,12 @@
         </is>
       </c>
       <c r="D553" s="4">
+        <v>50</v>
+      </c>
+      <c r="E553" s="4">
         <v>14</v>
       </c>
-      <c r="E553" s="6" t="inlineStr">
+      <c r="F553" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39541,9 +41203,12 @@
         </is>
       </c>
       <c r="D554" s="4">
+        <v>50</v>
+      </c>
+      <c r="E554" s="4">
         <v>15</v>
       </c>
-      <c r="E554" s="6" t="inlineStr">
+      <c r="F554" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39613,9 +41278,12 @@
         </is>
       </c>
       <c r="D555" s="4">
+        <v>50</v>
+      </c>
+      <c r="E555" s="4">
         <v>16</v>
       </c>
-      <c r="E555" s="6" t="inlineStr">
+      <c r="F555" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39685,9 +41353,12 @@
         </is>
       </c>
       <c r="D556" s="4">
+        <v>50</v>
+      </c>
+      <c r="E556" s="4">
         <v>17</v>
       </c>
-      <c r="E556" s="6" t="inlineStr">
+      <c r="F556" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39757,9 +41428,12 @@
         </is>
       </c>
       <c r="D557" s="4">
+        <v>50</v>
+      </c>
+      <c r="E557" s="4">
         <v>18</v>
       </c>
-      <c r="E557" s="6" t="inlineStr">
+      <c r="F557" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39829,9 +41503,12 @@
         </is>
       </c>
       <c r="D558" s="4">
+        <v>50</v>
+      </c>
+      <c r="E558" s="4">
         <v>19</v>
       </c>
-      <c r="E558" s="6" t="inlineStr">
+      <c r="F558" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39901,9 +41578,12 @@
         </is>
       </c>
       <c r="D559" s="4">
+        <v>50</v>
+      </c>
+      <c r="E559" s="4">
         <v>20</v>
       </c>
-      <c r="E559" s="6" t="inlineStr">
+      <c r="F559" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39973,9 +41653,12 @@
         </is>
       </c>
       <c r="D560" s="4">
+        <v>35</v>
+      </c>
+      <c r="E560" s="4">
         <v>1</v>
       </c>
-      <c r="E560" s="6" t="inlineStr">
+      <c r="F560" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40045,9 +41728,12 @@
         </is>
       </c>
       <c r="D561" s="4">
+        <v>35</v>
+      </c>
+      <c r="E561" s="4">
         <v>2</v>
       </c>
-      <c r="E561" s="6" t="inlineStr">
+      <c r="F561" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40117,9 +41803,12 @@
         </is>
       </c>
       <c r="D562" s="4">
+        <v>35</v>
+      </c>
+      <c r="E562" s="4">
         <v>3</v>
       </c>
-      <c r="E562" s="6" t="inlineStr">
+      <c r="F562" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40189,9 +41878,12 @@
         </is>
       </c>
       <c r="D563" s="4">
+        <v>35</v>
+      </c>
+      <c r="E563" s="4">
         <v>4</v>
       </c>
-      <c r="E563" s="6" t="inlineStr">
+      <c r="F563" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40261,9 +41953,12 @@
         </is>
       </c>
       <c r="D564" s="4">
+        <v>35</v>
+      </c>
+      <c r="E564" s="4">
         <v>5</v>
       </c>
-      <c r="E564" s="6" t="inlineStr">
+      <c r="F564" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40333,9 +42028,12 @@
         </is>
       </c>
       <c r="D565" s="4">
+        <v>35</v>
+      </c>
+      <c r="E565" s="4">
         <v>6</v>
       </c>
-      <c r="E565" s="6" t="inlineStr">
+      <c r="F565" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40405,9 +42103,12 @@
         </is>
       </c>
       <c r="D566" s="4">
+        <v>35</v>
+      </c>
+      <c r="E566" s="4">
         <v>7</v>
       </c>
-      <c r="E566" s="6" t="inlineStr">
+      <c r="F566" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40477,9 +42178,12 @@
         </is>
       </c>
       <c r="D567" s="4">
+        <v>35</v>
+      </c>
+      <c r="E567" s="4">
         <v>8</v>
       </c>
-      <c r="E567" s="6" t="inlineStr">
+      <c r="F567" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40549,9 +42253,12 @@
         </is>
       </c>
       <c r="D568" s="4">
+        <v>35</v>
+      </c>
+      <c r="E568" s="4">
         <v>9</v>
       </c>
-      <c r="E568" s="6" t="inlineStr">
+      <c r="F568" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40621,9 +42328,12 @@
         </is>
       </c>
       <c r="D569" s="4">
+        <v>35</v>
+      </c>
+      <c r="E569" s="4">
         <v>10</v>
       </c>
-      <c r="E569" s="6" t="inlineStr">
+      <c r="F569" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40693,9 +42403,12 @@
         </is>
       </c>
       <c r="D570" s="4">
+        <v>35</v>
+      </c>
+      <c r="E570" s="4">
         <v>11</v>
       </c>
-      <c r="E570" s="6" t="inlineStr">
+      <c r="F570" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40765,9 +42478,12 @@
         </is>
       </c>
       <c r="D571" s="4">
+        <v>35</v>
+      </c>
+      <c r="E571" s="4">
         <v>12</v>
       </c>
-      <c r="E571" s="6" t="inlineStr">
+      <c r="F571" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40837,9 +42553,12 @@
         </is>
       </c>
       <c r="D572" s="4">
+        <v>35</v>
+      </c>
+      <c r="E572" s="4">
         <v>13</v>
       </c>
-      <c r="E572" s="6" t="inlineStr">
+      <c r="F572" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40909,9 +42628,12 @@
         </is>
       </c>
       <c r="D573" s="4">
+        <v>35</v>
+      </c>
+      <c r="E573" s="4">
         <v>14</v>
       </c>
-      <c r="E573" s="6" t="inlineStr">
+      <c r="F573" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40981,9 +42703,12 @@
         </is>
       </c>
       <c r="D574" s="4">
+        <v>35</v>
+      </c>
+      <c r="E574" s="4">
         <v>15</v>
       </c>
-      <c r="E574" s="6" t="inlineStr">
+      <c r="F574" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41053,9 +42778,12 @@
         </is>
       </c>
       <c r="D575" s="4">
+        <v>35</v>
+      </c>
+      <c r="E575" s="4">
         <v>16</v>
       </c>
-      <c r="E575" s="6" t="inlineStr">
+      <c r="F575" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41125,9 +42853,12 @@
         </is>
       </c>
       <c r="D576" s="4">
+        <v>35</v>
+      </c>
+      <c r="E576" s="4">
         <v>17</v>
       </c>
-      <c r="E576" s="6" t="inlineStr">
+      <c r="F576" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41197,9 +42928,12 @@
         </is>
       </c>
       <c r="D577" s="4">
+        <v>35</v>
+      </c>
+      <c r="E577" s="4">
         <v>18</v>
       </c>
-      <c r="E577" s="6" t="inlineStr">
+      <c r="F577" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41269,9 +43003,12 @@
         </is>
       </c>
       <c r="D578" s="4">
+        <v>35</v>
+      </c>
+      <c r="E578" s="4">
         <v>19</v>
       </c>
-      <c r="E578" s="6" t="inlineStr">
+      <c r="F578" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41341,9 +43078,12 @@
         </is>
       </c>
       <c r="D579" s="4">
+        <v>35</v>
+      </c>
+      <c r="E579" s="4">
         <v>20</v>
       </c>
-      <c r="E579" s="6" t="inlineStr">
+      <c r="F579" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41413,9 +43153,12 @@
         </is>
       </c>
       <c r="D580" s="4">
+        <v>17</v>
+      </c>
+      <c r="E580" s="4">
         <v>1</v>
       </c>
-      <c r="E580" s="6" t="inlineStr">
+      <c r="F580" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41485,9 +43228,12 @@
         </is>
       </c>
       <c r="D581" s="4">
+        <v>17</v>
+      </c>
+      <c r="E581" s="4">
         <v>2</v>
       </c>
-      <c r="E581" s="6" t="inlineStr">
+      <c r="F581" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41557,9 +43303,12 @@
         </is>
       </c>
       <c r="D582" s="4">
+        <v>17</v>
+      </c>
+      <c r="E582" s="4">
         <v>3</v>
       </c>
-      <c r="E582" s="6" t="inlineStr">
+      <c r="F582" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41629,9 +43378,12 @@
         </is>
       </c>
       <c r="D583" s="4">
+        <v>17</v>
+      </c>
+      <c r="E583" s="4">
         <v>4</v>
       </c>
-      <c r="E583" s="6" t="inlineStr">
+      <c r="F583" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41701,9 +43453,12 @@
         </is>
       </c>
       <c r="D584" s="4">
+        <v>17</v>
+      </c>
+      <c r="E584" s="4">
         <v>5</v>
       </c>
-      <c r="E584" s="6" t="inlineStr">
+      <c r="F584" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41773,9 +43528,12 @@
         </is>
       </c>
       <c r="D585" s="4">
+        <v>17</v>
+      </c>
+      <c r="E585" s="4">
         <v>6</v>
       </c>
-      <c r="E585" s="6" t="inlineStr">
+      <c r="F585" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41845,9 +43603,12 @@
         </is>
       </c>
       <c r="D586" s="4">
+        <v>17</v>
+      </c>
+      <c r="E586" s="4">
         <v>7</v>
       </c>
-      <c r="E586" s="6" t="inlineStr">
+      <c r="F586" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41917,9 +43678,12 @@
         </is>
       </c>
       <c r="D587" s="4">
+        <v>17</v>
+      </c>
+      <c r="E587" s="4">
         <v>8</v>
       </c>
-      <c r="E587" s="6" t="inlineStr">
+      <c r="F587" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41989,9 +43753,12 @@
         </is>
       </c>
       <c r="D588" s="4">
+        <v>17</v>
+      </c>
+      <c r="E588" s="4">
         <v>9</v>
       </c>
-      <c r="E588" s="6" t="inlineStr">
+      <c r="F588" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42061,9 +43828,12 @@
         </is>
       </c>
       <c r="D589" s="4">
+        <v>17</v>
+      </c>
+      <c r="E589" s="4">
         <v>10</v>
       </c>
-      <c r="E589" s="6" t="inlineStr">
+      <c r="F589" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42133,9 +43903,12 @@
         </is>
       </c>
       <c r="D590" s="4">
+        <v>17</v>
+      </c>
+      <c r="E590" s="4">
         <v>11</v>
       </c>
-      <c r="E590" s="6" t="inlineStr">
+      <c r="F590" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42205,9 +43978,12 @@
         </is>
       </c>
       <c r="D591" s="4">
+        <v>17</v>
+      </c>
+      <c r="E591" s="4">
         <v>12</v>
       </c>
-      <c r="E591" s="6" t="inlineStr">
+      <c r="F591" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42277,9 +44053,12 @@
         </is>
       </c>
       <c r="D592" s="4">
+        <v>17</v>
+      </c>
+      <c r="E592" s="4">
         <v>13</v>
       </c>
-      <c r="E592" s="6" t="inlineStr">
+      <c r="F592" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42349,9 +44128,12 @@
         </is>
       </c>
       <c r="D593" s="4">
+        <v>17</v>
+      </c>
+      <c r="E593" s="4">
         <v>14</v>
       </c>
-      <c r="E593" s="6" t="inlineStr">
+      <c r="F593" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42421,9 +44203,12 @@
         </is>
       </c>
       <c r="D594" s="4">
+        <v>17</v>
+      </c>
+      <c r="E594" s="4">
         <v>15</v>
       </c>
-      <c r="E594" s="6" t="inlineStr">
+      <c r="F594" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42493,9 +44278,12 @@
         </is>
       </c>
       <c r="D595" s="4">
+        <v>17</v>
+      </c>
+      <c r="E595" s="4">
         <v>16</v>
       </c>
-      <c r="E595" s="6" t="inlineStr">
+      <c r="F595" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42567,7 +44355,10 @@
       <c r="D596" s="4">
         <v>17</v>
       </c>
-      <c r="E596" s="6" t="inlineStr">
+      <c r="E596" s="4">
+        <v>17</v>
+      </c>
+      <c r="F596" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42637,9 +44428,12 @@
         </is>
       </c>
       <c r="D597" s="4">
+        <v>2</v>
+      </c>
+      <c r="E597" s="4">
         <v>1</v>
       </c>
-      <c r="E597" s="6" t="inlineStr">
+      <c r="F597" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42711,7 +44505,10 @@
       <c r="D598" s="4">
         <v>2</v>
       </c>
-      <c r="E598" s="6" t="inlineStr">
+      <c r="E598" s="4">
+        <v>2</v>
+      </c>
+      <c r="F598" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42781,9 +44578,12 @@
         </is>
       </c>
       <c r="D599" s="4">
+        <v>4</v>
+      </c>
+      <c r="E599" s="4">
         <v>1</v>
       </c>
-      <c r="E599" s="6" t="inlineStr">
+      <c r="F599" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42853,9 +44653,12 @@
         </is>
       </c>
       <c r="D600" s="4">
+        <v>4</v>
+      </c>
+      <c r="E600" s="4">
         <v>2</v>
       </c>
-      <c r="E600" s="6" t="inlineStr">
+      <c r="F600" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42925,9 +44728,12 @@
         </is>
       </c>
       <c r="D601" s="4">
+        <v>4</v>
+      </c>
+      <c r="E601" s="4">
         <v>3</v>
       </c>
-      <c r="E601" s="6" t="inlineStr">
+      <c r="F601" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42999,7 +44805,10 @@
       <c r="D602" s="4">
         <v>4</v>
       </c>
-      <c r="E602" s="6" t="inlineStr">
+      <c r="E602" s="4">
+        <v>4</v>
+      </c>
+      <c r="F602" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43069,9 +44878,12 @@
         </is>
       </c>
       <c r="D603" s="4">
+        <v>5</v>
+      </c>
+      <c r="E603" s="4">
         <v>1</v>
       </c>
-      <c r="E603" s="6" t="inlineStr">
+      <c r="F603" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43141,9 +44953,12 @@
         </is>
       </c>
       <c r="D604" s="4">
+        <v>5</v>
+      </c>
+      <c r="E604" s="4">
         <v>2</v>
       </c>
-      <c r="E604" s="6" t="inlineStr">
+      <c r="F604" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43213,9 +45028,12 @@
         </is>
       </c>
       <c r="D605" s="4">
+        <v>5</v>
+      </c>
+      <c r="E605" s="4">
         <v>3</v>
       </c>
-      <c r="E605" s="6" t="inlineStr">
+      <c r="F605" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43285,9 +45103,12 @@
         </is>
       </c>
       <c r="D606" s="4">
+        <v>5</v>
+      </c>
+      <c r="E606" s="4">
         <v>4</v>
       </c>
-      <c r="E606" s="6" t="inlineStr">
+      <c r="F606" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43359,7 +45180,10 @@
       <c r="D607" s="4">
         <v>5</v>
       </c>
-      <c r="E607" s="6" t="inlineStr">
+      <c r="E607" s="4">
+        <v>5</v>
+      </c>
+      <c r="F607" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43413,373 +45237,495 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="366">
+  <mergeCells count="488">
     <mergeCell ref="A2:A6"/>
     <mergeCell ref="B2:B6"/>
     <mergeCell ref="C2:C6"/>
+    <mergeCell ref="D2:D6"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="C9:C11"/>
+    <mergeCell ref="D9:D11"/>
     <mergeCell ref="A12:A16"/>
     <mergeCell ref="B12:B16"/>
     <mergeCell ref="C12:C16"/>
+    <mergeCell ref="D12:D16"/>
     <mergeCell ref="A18:A21"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="C18:C21"/>
+    <mergeCell ref="D18:D21"/>
     <mergeCell ref="A22:A26"/>
     <mergeCell ref="B22:B26"/>
     <mergeCell ref="C22:C26"/>
+    <mergeCell ref="D22:D26"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="B28:B31"/>
     <mergeCell ref="C28:C31"/>
+    <mergeCell ref="D28:D31"/>
     <mergeCell ref="A32:A34"/>
     <mergeCell ref="B32:B34"/>
     <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="B35:B36"/>
     <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
     <mergeCell ref="A43:A44"/>
     <mergeCell ref="B43:B44"/>
     <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:D44"/>
     <mergeCell ref="A47:A50"/>
     <mergeCell ref="B47:B50"/>
     <mergeCell ref="C47:C50"/>
+    <mergeCell ref="D47:D50"/>
     <mergeCell ref="A51:A52"/>
     <mergeCell ref="B51:B52"/>
     <mergeCell ref="C51:C52"/>
+    <mergeCell ref="D51:D52"/>
     <mergeCell ref="A53:A57"/>
     <mergeCell ref="B53:B57"/>
     <mergeCell ref="C53:C57"/>
+    <mergeCell ref="D53:D57"/>
     <mergeCell ref="A58:A62"/>
     <mergeCell ref="B58:B62"/>
     <mergeCell ref="C58:C62"/>
+    <mergeCell ref="D58:D62"/>
     <mergeCell ref="A64:A67"/>
     <mergeCell ref="B64:B67"/>
     <mergeCell ref="C64:C67"/>
+    <mergeCell ref="D64:D67"/>
     <mergeCell ref="A68:A71"/>
     <mergeCell ref="B68:B71"/>
     <mergeCell ref="C68:C71"/>
+    <mergeCell ref="D68:D71"/>
     <mergeCell ref="A73:A74"/>
     <mergeCell ref="B73:B74"/>
     <mergeCell ref="C73:C74"/>
+    <mergeCell ref="D73:D74"/>
     <mergeCell ref="A76:A77"/>
     <mergeCell ref="B76:B77"/>
     <mergeCell ref="C76:C77"/>
+    <mergeCell ref="D76:D77"/>
     <mergeCell ref="A78:A79"/>
     <mergeCell ref="B78:B79"/>
     <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D78:D79"/>
     <mergeCell ref="A82:A86"/>
     <mergeCell ref="B82:B86"/>
     <mergeCell ref="C82:C86"/>
+    <mergeCell ref="D82:D86"/>
     <mergeCell ref="A88:A92"/>
     <mergeCell ref="B88:B92"/>
     <mergeCell ref="C88:C92"/>
+    <mergeCell ref="D88:D92"/>
     <mergeCell ref="A93:A97"/>
     <mergeCell ref="B93:B97"/>
     <mergeCell ref="C93:C97"/>
+    <mergeCell ref="D93:D97"/>
     <mergeCell ref="A98:A99"/>
     <mergeCell ref="B98:B99"/>
     <mergeCell ref="C98:C99"/>
+    <mergeCell ref="D98:D99"/>
     <mergeCell ref="A100:A104"/>
     <mergeCell ref="B100:B104"/>
     <mergeCell ref="C100:C104"/>
+    <mergeCell ref="D100:D104"/>
     <mergeCell ref="A105:A109"/>
     <mergeCell ref="B105:B109"/>
     <mergeCell ref="C105:C109"/>
+    <mergeCell ref="D105:D109"/>
     <mergeCell ref="A111:A113"/>
     <mergeCell ref="B111:B113"/>
     <mergeCell ref="C111:C113"/>
+    <mergeCell ref="D111:D113"/>
     <mergeCell ref="A114:A115"/>
     <mergeCell ref="B114:B115"/>
     <mergeCell ref="C114:C115"/>
+    <mergeCell ref="D114:D115"/>
     <mergeCell ref="A118:A120"/>
     <mergeCell ref="B118:B120"/>
     <mergeCell ref="C118:C120"/>
+    <mergeCell ref="D118:D120"/>
     <mergeCell ref="A122:A126"/>
     <mergeCell ref="B122:B126"/>
     <mergeCell ref="C122:C126"/>
+    <mergeCell ref="D122:D126"/>
     <mergeCell ref="A127:A130"/>
     <mergeCell ref="B127:B130"/>
     <mergeCell ref="C127:C130"/>
+    <mergeCell ref="D127:D130"/>
     <mergeCell ref="A133:A137"/>
     <mergeCell ref="B133:B137"/>
     <mergeCell ref="C133:C137"/>
+    <mergeCell ref="D133:D137"/>
     <mergeCell ref="A138:A142"/>
     <mergeCell ref="B138:B142"/>
     <mergeCell ref="C138:C142"/>
+    <mergeCell ref="D138:D142"/>
     <mergeCell ref="A143:A147"/>
     <mergeCell ref="B143:B147"/>
     <mergeCell ref="C143:C147"/>
+    <mergeCell ref="D143:D147"/>
     <mergeCell ref="A149:A151"/>
     <mergeCell ref="B149:B151"/>
     <mergeCell ref="C149:C151"/>
+    <mergeCell ref="D149:D151"/>
     <mergeCell ref="A152:A153"/>
     <mergeCell ref="B152:B153"/>
     <mergeCell ref="C152:C153"/>
+    <mergeCell ref="D152:D153"/>
     <mergeCell ref="A154:A155"/>
     <mergeCell ref="B154:B155"/>
     <mergeCell ref="C154:C155"/>
+    <mergeCell ref="D154:D155"/>
     <mergeCell ref="A157:A158"/>
     <mergeCell ref="B157:B158"/>
     <mergeCell ref="C157:C158"/>
+    <mergeCell ref="D157:D158"/>
     <mergeCell ref="A159:A160"/>
     <mergeCell ref="B159:B160"/>
     <mergeCell ref="C159:C160"/>
+    <mergeCell ref="D159:D160"/>
     <mergeCell ref="A164:A165"/>
     <mergeCell ref="B164:B165"/>
     <mergeCell ref="C164:C165"/>
+    <mergeCell ref="D164:D165"/>
     <mergeCell ref="A168:A172"/>
     <mergeCell ref="B168:B172"/>
     <mergeCell ref="C168:C172"/>
+    <mergeCell ref="D168:D172"/>
     <mergeCell ref="A173:A176"/>
     <mergeCell ref="B173:B176"/>
     <mergeCell ref="C173:C176"/>
+    <mergeCell ref="D173:D176"/>
     <mergeCell ref="A177:A181"/>
     <mergeCell ref="B177:B181"/>
     <mergeCell ref="C177:C181"/>
+    <mergeCell ref="D177:D181"/>
     <mergeCell ref="A182:A183"/>
     <mergeCell ref="B182:B183"/>
     <mergeCell ref="C182:C183"/>
+    <mergeCell ref="D182:D183"/>
     <mergeCell ref="A187:A189"/>
     <mergeCell ref="B187:B189"/>
     <mergeCell ref="C187:C189"/>
+    <mergeCell ref="D187:D189"/>
     <mergeCell ref="A190:A191"/>
     <mergeCell ref="B190:B191"/>
     <mergeCell ref="C190:C191"/>
+    <mergeCell ref="D190:D191"/>
     <mergeCell ref="A192:A195"/>
     <mergeCell ref="B192:B195"/>
     <mergeCell ref="C192:C195"/>
+    <mergeCell ref="D192:D195"/>
     <mergeCell ref="A199:A200"/>
     <mergeCell ref="B199:B200"/>
     <mergeCell ref="C199:C200"/>
+    <mergeCell ref="D199:D200"/>
     <mergeCell ref="A202:A203"/>
     <mergeCell ref="B202:B203"/>
     <mergeCell ref="C202:C203"/>
+    <mergeCell ref="D202:D203"/>
     <mergeCell ref="A205:A206"/>
     <mergeCell ref="B205:B206"/>
     <mergeCell ref="C205:C206"/>
+    <mergeCell ref="D205:D206"/>
     <mergeCell ref="A209:A210"/>
     <mergeCell ref="B209:B210"/>
     <mergeCell ref="C209:C210"/>
+    <mergeCell ref="D209:D210"/>
     <mergeCell ref="A214:A216"/>
     <mergeCell ref="B214:B216"/>
     <mergeCell ref="C214:C216"/>
+    <mergeCell ref="D214:D216"/>
     <mergeCell ref="A217:A218"/>
     <mergeCell ref="B217:B218"/>
     <mergeCell ref="C217:C218"/>
+    <mergeCell ref="D217:D218"/>
     <mergeCell ref="A222:A223"/>
     <mergeCell ref="B222:B223"/>
     <mergeCell ref="C222:C223"/>
+    <mergeCell ref="D222:D223"/>
     <mergeCell ref="A225:A226"/>
     <mergeCell ref="B225:B226"/>
     <mergeCell ref="C225:C226"/>
+    <mergeCell ref="D225:D226"/>
     <mergeCell ref="A227:A229"/>
     <mergeCell ref="B227:B229"/>
     <mergeCell ref="C227:C229"/>
+    <mergeCell ref="D227:D229"/>
     <mergeCell ref="A240:A241"/>
     <mergeCell ref="B240:B241"/>
     <mergeCell ref="C240:C241"/>
+    <mergeCell ref="D240:D241"/>
     <mergeCell ref="A242:A243"/>
     <mergeCell ref="B242:B243"/>
     <mergeCell ref="C242:C243"/>
+    <mergeCell ref="D242:D243"/>
     <mergeCell ref="A244:A248"/>
     <mergeCell ref="B244:B248"/>
     <mergeCell ref="C244:C248"/>
+    <mergeCell ref="D244:D248"/>
     <mergeCell ref="A249:A250"/>
     <mergeCell ref="B249:B250"/>
     <mergeCell ref="C249:C250"/>
+    <mergeCell ref="D249:D250"/>
     <mergeCell ref="A251:A254"/>
     <mergeCell ref="B251:B254"/>
     <mergeCell ref="C251:C254"/>
+    <mergeCell ref="D251:D254"/>
     <mergeCell ref="A255:A258"/>
     <mergeCell ref="B255:B258"/>
     <mergeCell ref="C255:C258"/>
+    <mergeCell ref="D255:D258"/>
     <mergeCell ref="A263:A265"/>
     <mergeCell ref="B263:B265"/>
     <mergeCell ref="C263:C265"/>
+    <mergeCell ref="D263:D265"/>
     <mergeCell ref="A267:A269"/>
     <mergeCell ref="B267:B269"/>
     <mergeCell ref="C267:C269"/>
+    <mergeCell ref="D267:D269"/>
     <mergeCell ref="A270:A272"/>
     <mergeCell ref="B270:B272"/>
     <mergeCell ref="C270:C272"/>
+    <mergeCell ref="D270:D272"/>
     <mergeCell ref="A274:A278"/>
     <mergeCell ref="B274:B278"/>
     <mergeCell ref="C274:C278"/>
+    <mergeCell ref="D274:D278"/>
     <mergeCell ref="A279:A280"/>
     <mergeCell ref="B279:B280"/>
     <mergeCell ref="C279:C280"/>
+    <mergeCell ref="D279:D280"/>
     <mergeCell ref="A281:A283"/>
     <mergeCell ref="B281:B283"/>
     <mergeCell ref="C281:C283"/>
+    <mergeCell ref="D281:D283"/>
     <mergeCell ref="A284:A288"/>
     <mergeCell ref="B284:B288"/>
     <mergeCell ref="C284:C288"/>
+    <mergeCell ref="D284:D288"/>
     <mergeCell ref="A290:A291"/>
     <mergeCell ref="B290:B291"/>
     <mergeCell ref="C290:C291"/>
+    <mergeCell ref="D290:D291"/>
     <mergeCell ref="A292:A293"/>
     <mergeCell ref="B292:B293"/>
     <mergeCell ref="C292:C293"/>
+    <mergeCell ref="D292:D293"/>
     <mergeCell ref="A296:A299"/>
     <mergeCell ref="B296:B299"/>
     <mergeCell ref="C296:C299"/>
+    <mergeCell ref="D296:D299"/>
     <mergeCell ref="A300:A301"/>
     <mergeCell ref="B300:B301"/>
     <mergeCell ref="C300:C301"/>
+    <mergeCell ref="D300:D301"/>
     <mergeCell ref="A302:A306"/>
     <mergeCell ref="B302:B306"/>
     <mergeCell ref="C302:C306"/>
+    <mergeCell ref="D302:D306"/>
     <mergeCell ref="A307:A308"/>
     <mergeCell ref="B307:B308"/>
     <mergeCell ref="C307:C308"/>
+    <mergeCell ref="D307:D308"/>
     <mergeCell ref="A313:A314"/>
     <mergeCell ref="B313:B314"/>
     <mergeCell ref="C313:C314"/>
+    <mergeCell ref="D313:D314"/>
     <mergeCell ref="A322:A325"/>
     <mergeCell ref="B322:B325"/>
     <mergeCell ref="C322:C325"/>
+    <mergeCell ref="D322:D325"/>
     <mergeCell ref="A326:A327"/>
     <mergeCell ref="B326:B327"/>
     <mergeCell ref="C326:C327"/>
+    <mergeCell ref="D326:D327"/>
     <mergeCell ref="A329:A332"/>
     <mergeCell ref="B329:B332"/>
     <mergeCell ref="C329:C332"/>
+    <mergeCell ref="D329:D332"/>
     <mergeCell ref="A333:A334"/>
     <mergeCell ref="B333:B334"/>
     <mergeCell ref="C333:C334"/>
+    <mergeCell ref="D333:D334"/>
     <mergeCell ref="A337:A338"/>
     <mergeCell ref="B337:B338"/>
     <mergeCell ref="C337:C338"/>
+    <mergeCell ref="D337:D338"/>
     <mergeCell ref="A339:A340"/>
     <mergeCell ref="B339:B340"/>
     <mergeCell ref="C339:C340"/>
+    <mergeCell ref="D339:D340"/>
     <mergeCell ref="A343:A344"/>
     <mergeCell ref="B343:B344"/>
     <mergeCell ref="C343:C344"/>
+    <mergeCell ref="D343:D344"/>
     <mergeCell ref="A350:A351"/>
     <mergeCell ref="B350:B351"/>
     <mergeCell ref="C350:C351"/>
+    <mergeCell ref="D350:D351"/>
     <mergeCell ref="A356:A359"/>
     <mergeCell ref="B356:B359"/>
     <mergeCell ref="C356:C359"/>
+    <mergeCell ref="D356:D359"/>
     <mergeCell ref="A360:A361"/>
     <mergeCell ref="B360:B361"/>
     <mergeCell ref="C360:C361"/>
+    <mergeCell ref="D360:D361"/>
     <mergeCell ref="A366:A368"/>
     <mergeCell ref="B366:B368"/>
     <mergeCell ref="C366:C368"/>
+    <mergeCell ref="D366:D368"/>
     <mergeCell ref="A371:A379"/>
     <mergeCell ref="B371:B379"/>
     <mergeCell ref="C371:C379"/>
+    <mergeCell ref="D371:D379"/>
     <mergeCell ref="A380:A385"/>
     <mergeCell ref="B380:B385"/>
     <mergeCell ref="C380:C385"/>
+    <mergeCell ref="D380:D385"/>
     <mergeCell ref="A386:A387"/>
     <mergeCell ref="B386:B387"/>
     <mergeCell ref="C386:C387"/>
+    <mergeCell ref="D386:D387"/>
     <mergeCell ref="A388:A393"/>
     <mergeCell ref="B388:B393"/>
     <mergeCell ref="C388:C393"/>
+    <mergeCell ref="D388:D393"/>
     <mergeCell ref="A394:A396"/>
     <mergeCell ref="B394:B396"/>
     <mergeCell ref="C394:C396"/>
+    <mergeCell ref="D394:D396"/>
     <mergeCell ref="A397:A398"/>
     <mergeCell ref="B397:B398"/>
     <mergeCell ref="C397:C398"/>
+    <mergeCell ref="D397:D398"/>
     <mergeCell ref="A399:A401"/>
     <mergeCell ref="B399:B401"/>
     <mergeCell ref="C399:C401"/>
+    <mergeCell ref="D399:D401"/>
     <mergeCell ref="A402:A421"/>
     <mergeCell ref="B402:B421"/>
     <mergeCell ref="C402:C421"/>
+    <mergeCell ref="D402:D421"/>
     <mergeCell ref="A422:A424"/>
     <mergeCell ref="B422:B424"/>
     <mergeCell ref="C422:C424"/>
+    <mergeCell ref="D422:D424"/>
     <mergeCell ref="A427:A439"/>
     <mergeCell ref="B427:B439"/>
     <mergeCell ref="C427:C439"/>
+    <mergeCell ref="D427:D439"/>
     <mergeCell ref="A440:A443"/>
     <mergeCell ref="B440:B443"/>
     <mergeCell ref="C440:C443"/>
+    <mergeCell ref="D440:D443"/>
     <mergeCell ref="A446:A449"/>
     <mergeCell ref="B446:B449"/>
     <mergeCell ref="C446:C449"/>
+    <mergeCell ref="D446:D449"/>
     <mergeCell ref="A453:A459"/>
     <mergeCell ref="B453:B459"/>
     <mergeCell ref="C453:C459"/>
+    <mergeCell ref="D453:D459"/>
     <mergeCell ref="A464:A466"/>
     <mergeCell ref="B464:B466"/>
     <mergeCell ref="C464:C466"/>
+    <mergeCell ref="D464:D466"/>
     <mergeCell ref="A467:A468"/>
     <mergeCell ref="B467:B468"/>
     <mergeCell ref="C467:C468"/>
+    <mergeCell ref="D467:D468"/>
     <mergeCell ref="A469:A471"/>
     <mergeCell ref="B469:B471"/>
     <mergeCell ref="C469:C471"/>
+    <mergeCell ref="D469:D471"/>
     <mergeCell ref="A475:A476"/>
     <mergeCell ref="B475:B476"/>
     <mergeCell ref="C475:C476"/>
+    <mergeCell ref="D475:D476"/>
     <mergeCell ref="A477:A478"/>
     <mergeCell ref="B477:B478"/>
     <mergeCell ref="C477:C478"/>
+    <mergeCell ref="D477:D478"/>
     <mergeCell ref="A479:A480"/>
     <mergeCell ref="B479:B480"/>
     <mergeCell ref="C479:C480"/>
+    <mergeCell ref="D479:D480"/>
     <mergeCell ref="A484:A485"/>
     <mergeCell ref="B484:B485"/>
     <mergeCell ref="C484:C485"/>
+    <mergeCell ref="D484:D485"/>
     <mergeCell ref="A487:A499"/>
     <mergeCell ref="B487:B499"/>
     <mergeCell ref="C487:C499"/>
+    <mergeCell ref="D487:D499"/>
     <mergeCell ref="A500:A507"/>
     <mergeCell ref="B500:B507"/>
     <mergeCell ref="C500:C507"/>
+    <mergeCell ref="D500:D507"/>
     <mergeCell ref="A508:A513"/>
     <mergeCell ref="B508:B513"/>
     <mergeCell ref="C508:C513"/>
+    <mergeCell ref="D508:D513"/>
     <mergeCell ref="A514:A518"/>
     <mergeCell ref="B514:B518"/>
     <mergeCell ref="C514:C518"/>
+    <mergeCell ref="D514:D518"/>
     <mergeCell ref="A519:A524"/>
     <mergeCell ref="B519:B524"/>
     <mergeCell ref="C519:C524"/>
+    <mergeCell ref="D519:D524"/>
     <mergeCell ref="A525:A527"/>
     <mergeCell ref="B525:B527"/>
     <mergeCell ref="C525:C527"/>
+    <mergeCell ref="D525:D527"/>
     <mergeCell ref="A528:A530"/>
     <mergeCell ref="B528:B530"/>
     <mergeCell ref="C528:C530"/>
+    <mergeCell ref="D528:D530"/>
     <mergeCell ref="A531:A533"/>
     <mergeCell ref="B531:B533"/>
     <mergeCell ref="C531:C533"/>
+    <mergeCell ref="D531:D533"/>
     <mergeCell ref="A534:A535"/>
     <mergeCell ref="B534:B535"/>
     <mergeCell ref="C534:C535"/>
+    <mergeCell ref="D534:D535"/>
     <mergeCell ref="A537:A538"/>
     <mergeCell ref="B537:B538"/>
     <mergeCell ref="C537:C538"/>
+    <mergeCell ref="D537:D538"/>
     <mergeCell ref="A540:A559"/>
     <mergeCell ref="B540:B559"/>
     <mergeCell ref="C540:C559"/>
+    <mergeCell ref="D540:D559"/>
     <mergeCell ref="A560:A579"/>
     <mergeCell ref="B560:B579"/>
     <mergeCell ref="C560:C579"/>
+    <mergeCell ref="D560:D579"/>
     <mergeCell ref="A580:A596"/>
     <mergeCell ref="B580:B596"/>
     <mergeCell ref="C580:C596"/>
+    <mergeCell ref="D580:D596"/>
     <mergeCell ref="A597:A598"/>
     <mergeCell ref="B597:B598"/>
     <mergeCell ref="C597:C598"/>
+    <mergeCell ref="D597:D598"/>
     <mergeCell ref="A599:A602"/>
     <mergeCell ref="B599:B602"/>
     <mergeCell ref="C599:C602"/>
+    <mergeCell ref="D599:D602"/>
     <mergeCell ref="A603:A607"/>
     <mergeCell ref="B603:B607"/>
     <mergeCell ref="C603:C607"/>
+    <mergeCell ref="D603:D607"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
